--- a/BELGRANO 1646/Noviembre/Noviembre-BLG1646.xlsx
+++ b/BELGRANO 1646/Noviembre/Noviembre-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C4985F-A88B-42E5-AB8D-2C1151D8EE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EC2A0F-B361-41A9-9BA0-EC62B236F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="176">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -523,27 +523,12 @@
     <t>GASTOS PARTICULARES</t>
   </si>
   <si>
-    <t>VTO: 14/11</t>
-  </si>
-  <si>
-    <t>Sa - Seguridad - Servicio tecnico zona A - Balun</t>
-  </si>
-  <si>
     <t>Contessi - Provision y colocacion de tres tubos de luz led en cabinas de los acensores</t>
   </si>
   <si>
     <t>Ferreteria el herrero - Lamparas, pico, pinceleta, rodillo, aguarras x3, cinta, silicona, etc</t>
   </si>
   <si>
-    <t>PERÍODO: OCTUBRE</t>
-  </si>
-  <si>
-    <t>Honorarios OCTUBRE</t>
-  </si>
-  <si>
-    <t>Ingreso mes de SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Numero 1859135 Debito automatico 01/10</t>
   </si>
   <si>
@@ -557,9 +542,6 @@
   </si>
   <si>
     <t>Debito 13/10</t>
-  </si>
-  <si>
-    <t>Luis Barrazza - Colocacion de porcelanatos - UF 27 y 29</t>
   </si>
   <si>
     <t>Debito 24/10</t>
@@ -585,6 +567,30 @@
   <si>
     <t>Las expensas extraordinarias ascendieron a un total de $2.900.000. Sin embargo, considerando que pasar de un prorrateo de $450.000 a dicho monto implicaría un incremento significativo en el valor final de las expensas, se resolvió distribuir este importe en tres cuotas.
 Por lo tanto, en el presente período se prorratea una tercera parte del monto total correspondiente a las extraordinarias, con el fin de mantener un equilibrio en los valores a abonar.</t>
+  </si>
+  <si>
+    <t>VTO: 15/12</t>
+  </si>
+  <si>
+    <t>PERÍODO: NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Honorarios NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Ingreso mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>Servisur - 10 plafones 12w en escaleras y 5</t>
+  </si>
+  <si>
+    <t>Distribuidora Barbieiro</t>
+  </si>
+  <si>
+    <t>Pintureria Ogus - Sinteplast, Albaalatex, pincel, Enduido, etc</t>
+  </si>
+  <si>
+    <t>Gamboa gustavo - Trabajo realizado - Limpieza de zona afectada en zingueria, sellado de grietas con filtraciones con membrana transparente</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1318,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1573,192 +1579,14 @@
     <xf numFmtId="167" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="15" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="6" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="6" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="6" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1770,6 +1598,188 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2135,24 +2145,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P130"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P134"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8"/>
       <c r="B1" s="96" t="s">
         <v>118</v>
@@ -2161,7 +2171,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
         <v>0</v>
@@ -2170,7 +2180,7 @@
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="s">
         <v>88</v>
@@ -2179,7 +2189,7 @@
       <c r="D3" s="67"/>
       <c r="E3" s="68"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="66"/>
       <c r="B4" s="67" t="s">
         <v>89</v>
@@ -2188,20 +2198,20 @@
       <c r="D4" s="67"/>
       <c r="E4" s="68"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="70" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D5" s="70"/>
       <c r="E5" s="71"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="66" t="s">
         <v>99</v>
       </c>
@@ -2210,7 +2220,7 @@
       <c r="D6" s="67"/>
       <c r="E6" s="68"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="69" t="s">
         <v>98</v>
       </c>
@@ -2219,37 +2229,37 @@
       <c r="D7" s="70"/>
       <c r="E7" s="71"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="188" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="201" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="189"/>
-      <c r="D14" s="190"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="191"/>
-      <c r="C15" s="192"/>
-      <c r="D15" s="193"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="191"/>
-      <c r="C16" s="192"/>
-      <c r="D16" s="193"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="194"/>
-      <c r="C17" s="195"/>
-      <c r="D17" s="196"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="202"/>
+      <c r="D14" s="203"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="204"/>
+      <c r="C15" s="205"/>
+      <c r="D15" s="206"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="204"/>
+      <c r="C16" s="205"/>
+      <c r="D16" s="206"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="207"/>
+      <c r="C17" s="208"/>
+      <c r="D17" s="209"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="60" t="s">
         <v>86</v>
       </c>
@@ -2263,19 +2273,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="119" t="s">
         <v>142</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="125"/>
       <c r="E22" s="176"/>
       <c r="F22" s="176"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="119" t="s">
         <v>126</v>
       </c>
@@ -2293,7 +2303,7 @@
         <v>111350.42022</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="119" t="s">
         <v>2</v>
       </c>
@@ -2311,7 +2321,7 @@
         <v>-24218.716681000002</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="119" t="s">
         <v>112</v>
       </c>
@@ -2329,7 +2339,7 @@
         <v>2.3460999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="119"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2337,7 +2347,7 @@
       <c r="E26" s="129"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="94" t="s">
         <v>3</v>
       </c>
@@ -2364,7 +2374,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="93" t="s">
         <v>109</v>
       </c>
@@ -2383,7 +2393,7 @@
       </c>
       <c r="H28" s="142"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="93"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2400,7 +2410,7 @@
       </c>
       <c r="H29" s="142"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="93"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -2409,7 +2419,7 @@
       <c r="F30" s="7"/>
       <c r="H30" s="142"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="93"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -2418,7 +2428,7 @@
       <c r="F31" s="7"/>
       <c r="H31" s="142"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="94" t="s">
         <v>117</v>
       </c>
@@ -2445,7 +2455,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="93" t="s">
         <v>109</v>
       </c>
@@ -2462,7 +2472,7 @@
       </c>
       <c r="H33" s="142"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
@@ -2479,7 +2489,7 @@
       </c>
       <c r="H34" s="142"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="93" t="s">
         <v>2</v>
       </c>
@@ -2496,7 +2506,7 @@
       </c>
       <c r="H35" s="142"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="94" t="s">
         <v>110</v>
       </c>
@@ -2516,7 +2526,7 @@
       </c>
       <c r="H36" s="142"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="124"/>
       <c r="B37" s="97"/>
       <c r="C37" s="97"/>
@@ -2525,7 +2535,7 @@
       <c r="F37" s="118"/>
       <c r="H37" s="142"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="124"/>
       <c r="B38" s="97"/>
       <c r="C38" s="97"/>
@@ -2534,7 +2544,7 @@
       <c r="F38" s="118"/>
       <c r="H38" s="142"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="97"/>
       <c r="B39" s="97"/>
       <c r="C39" s="109"/>
@@ -2543,7 +2553,7 @@
       <c r="F39" s="118"/>
       <c r="H39" s="142"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="94" t="s">
         <v>117</v>
       </c>
@@ -2560,7 +2570,7 @@
       </c>
       <c r="H40" s="142"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="93"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -2575,7 +2585,7 @@
       </c>
       <c r="H41" s="142"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="93"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2590,7 +2600,7 @@
       </c>
       <c r="H42" s="142"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="93"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -2605,7 +2615,7 @@
       </c>
       <c r="H43" s="142"/>
     </row>
-    <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="94" t="s">
         <v>127</v>
       </c>
@@ -2629,7 +2639,7 @@
       </c>
       <c r="H44" s="142"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="93" t="s">
         <v>4</v>
       </c>
@@ -2640,9 +2650,9 @@
       <c r="F45" s="99"/>
       <c r="H45" s="142"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="93" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="97"/>
@@ -2659,51 +2669,50 @@
       </c>
       <c r="H46" s="142"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="93" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="111">
-        <f>113583.37+6781.8+61036.17</f>
-        <v>181401.34</v>
+      <c r="D47" s="173">
+        <f>115317.73+6881.98+61937.82</f>
+        <v>184137.53</v>
       </c>
       <c r="E47" s="129">
         <f>D47*91.91%</f>
-        <v>166725.97159399997</v>
+        <v>169240.80382299999</v>
       </c>
       <c r="F47" s="129">
         <f>D47*8.09%</f>
-        <v>14675.368406</v>
+        <v>14896.726177</v>
       </c>
       <c r="H47" s="142"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="93" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="97" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="111">
-        <f>600931.76+14011.05</f>
-        <v>614942.81000000006</v>
+      <c r="D48" s="173">
+        <v>609845.93000000005</v>
       </c>
       <c r="E48" s="129">
         <f>D48*91.91%</f>
-        <v>565193.93667099997</v>
+        <v>560509.39426299999</v>
       </c>
       <c r="F48" s="129">
         <f>D48*8.09%</f>
-        <v>49748.873329000002</v>
+        <v>49336.535737000006</v>
       </c>
       <c r="H48" s="142"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="94" t="s">
         <v>6</v>
       </c>
@@ -2711,26 +2720,26 @@
       <c r="C49" s="95"/>
       <c r="D49" s="106">
         <f>SUM(D46:D48)</f>
-        <v>801364.15</v>
+        <v>799003.46000000008</v>
       </c>
       <c r="E49" s="106">
         <f t="shared" ref="E49:F49" si="6">SUM(E46:E48)</f>
-        <v>736533.79026499996</v>
+        <v>734364.08008600003</v>
       </c>
       <c r="F49" s="106">
         <f t="shared" si="6"/>
-        <v>64830.359735000005</v>
+        <v>64639.379914000005</v>
       </c>
       <c r="G49" s="107">
         <f>E49+F49</f>
-        <v>801364.14999999991</v>
+        <v>799003.46000000008</v>
       </c>
       <c r="H49" s="142" t="str">
         <f>IF(D49=G49, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
@@ -2741,9 +2750,9 @@
       <c r="F50" s="7"/>
       <c r="H50" s="142"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="170" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B51" s="159"/>
       <c r="C51" s="160"/>
@@ -2766,13 +2775,13 @@
       <c r="I51" s="161"/>
       <c r="J51" s="161"/>
     </row>
-    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="170" t="s">
         <v>138</v>
       </c>
       <c r="B52" s="159"/>
       <c r="C52" s="160"/>
-      <c r="D52" s="111">
+      <c r="D52" s="173">
         <v>372000</v>
       </c>
       <c r="E52" s="141">
@@ -2794,258 +2803,227 @@
       </c>
       <c r="J52" s="161"/>
     </row>
-    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="119" t="s">
         <v>8</v>
       </c>
       <c r="B53" s="149"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="111"/>
+      <c r="D53" s="173">
+        <v>153143.35</v>
+      </c>
       <c r="E53" s="141">
-        <f t="shared" ref="E53:E58" si="7">D53*91.91%</f>
-        <v>0</v>
+        <f t="shared" ref="E53:E60" si="7">D53*91.91%</f>
+        <v>140754.05298499999</v>
       </c>
       <c r="F53" s="129">
-        <f t="shared" ref="F53:F58" si="8">D53*8.09%</f>
-        <v>0</v>
+        <f t="shared" ref="F53:F60" si="8">D53*8.09%</f>
+        <v>12389.297015</v>
       </c>
       <c r="G53" s="107">
-        <f t="shared" ref="G53:G63" si="9">D53</f>
-        <v>0</v>
+        <f t="shared" ref="G53:G67" si="9">D53</f>
+        <v>153143.35</v>
       </c>
       <c r="H53" s="148">
-        <f t="shared" ref="H53:H63" si="10">E53+F53</f>
-        <v>0</v>
+        <f t="shared" ref="H53:H67" si="10">E53+F53</f>
+        <v>153143.34999999998</v>
       </c>
       <c r="I53" s="161"/>
       <c r="J53" s="161"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="93" t="s">
-        <v>168</v>
-      </c>
-      <c r="B54" s="7"/>
+    <row r="54" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="262" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="149"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="111">
-        <v>148200</v>
-      </c>
-      <c r="E54" s="141">
-        <f t="shared" si="7"/>
-        <v>136210.62</v>
-      </c>
-      <c r="F54" s="129">
-        <f t="shared" si="8"/>
-        <v>11989.38</v>
-      </c>
-      <c r="G54" s="107">
-        <f t="shared" si="9"/>
-        <v>148200</v>
-      </c>
-      <c r="H54" s="148">
-        <f t="shared" si="10"/>
-        <v>148200</v>
-      </c>
-      <c r="I54" s="161">
-        <f t="shared" ref="I54:I62" si="11">H54-D54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="161">
-        <f t="shared" ref="J54:J62" si="12">G54-D54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="93" t="s">
-        <v>169</v>
-      </c>
-      <c r="B55" s="7"/>
+      <c r="D54" s="173">
+        <v>1132015.98</v>
+      </c>
+      <c r="E54" s="141"/>
+      <c r="F54" s="129"/>
+      <c r="G54" s="107"/>
+      <c r="H54" s="148"/>
+      <c r="I54" s="161"/>
+      <c r="J54" s="161"/>
+    </row>
+    <row r="55" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="262" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="149"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="111">
-        <v>812358.3</v>
-      </c>
-      <c r="E55" s="141">
-        <f t="shared" si="7"/>
-        <v>746638.51353</v>
-      </c>
-      <c r="F55" s="129">
-        <f t="shared" si="8"/>
-        <v>65719.786470000006</v>
-      </c>
-      <c r="G55" s="107">
-        <f t="shared" si="9"/>
-        <v>812358.3</v>
-      </c>
-      <c r="H55" s="148">
-        <f t="shared" si="10"/>
-        <v>812358.3</v>
-      </c>
+      <c r="D55" s="173">
+        <v>261299.98</v>
+      </c>
+      <c r="E55" s="141"/>
+      <c r="F55" s="129"/>
+      <c r="G55" s="107"/>
+      <c r="H55" s="148"/>
       <c r="I55" s="161"/>
       <c r="J55" s="161"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="93" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>160</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="B56" s="7"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="111">
-        <v>129320</v>
+      <c r="D56" s="173">
+        <v>120000</v>
       </c>
       <c r="E56" s="141">
-        <f>D56*91.91%</f>
-        <v>118858.01199999999</v>
+        <f t="shared" si="7"/>
+        <v>110291.99999999999</v>
       </c>
       <c r="F56" s="129">
         <f t="shared" si="8"/>
-        <v>10461.987999999999</v>
+        <v>9708</v>
       </c>
       <c r="G56" s="107">
         <f t="shared" si="9"/>
-        <v>129320</v>
+        <v>120000</v>
       </c>
       <c r="H56" s="148">
-        <f>E56+F56</f>
-        <v>129319.99999999999</v>
+        <f t="shared" si="10"/>
+        <v>119999.99999999999</v>
       </c>
       <c r="I56" s="161">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="I56:I66" si="11">H56-D56</f>
         <v>0</v>
       </c>
       <c r="J56" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="97" t="s">
-        <v>161</v>
-      </c>
+        <f t="shared" ref="J56:J66" si="12">G56-D56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="261" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" s="7"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="111">
-        <v>655067.86</v>
+      <c r="D57" s="173">
+        <v>175450</v>
       </c>
       <c r="E57" s="141">
         <f t="shared" si="7"/>
-        <v>602072.87012599991</v>
+        <v>161256.09499999997</v>
       </c>
       <c r="F57" s="129">
         <f t="shared" si="8"/>
-        <v>52994.989873999999</v>
+        <v>14193.905000000001</v>
       </c>
       <c r="G57" s="107">
         <f t="shared" si="9"/>
-        <v>655067.86</v>
+        <v>175450</v>
       </c>
       <c r="H57" s="148">
         <f t="shared" si="10"/>
-        <v>655067.85999999987</v>
-      </c>
-      <c r="I57" s="161">
+        <v>175449.99999999997</v>
+      </c>
+      <c r="I57" s="161"/>
+      <c r="J57" s="161"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="111">
+        <v>129320</v>
+      </c>
+      <c r="E58" s="141">
+        <f>D58*91.91%</f>
+        <v>118858.01199999999</v>
+      </c>
+      <c r="F58" s="129">
+        <f t="shared" si="8"/>
+        <v>10461.987999999999</v>
+      </c>
+      <c r="G58" s="107">
+        <f t="shared" si="9"/>
+        <v>129320</v>
+      </c>
+      <c r="H58" s="148">
+        <f>E58+F58</f>
+        <v>129319.99999999999</v>
+      </c>
+      <c r="I58" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J57" s="161">
+      <c r="J58" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="124" t="s">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="173">
+        <v>655067.85</v>
+      </c>
+      <c r="E59" s="141">
+        <f t="shared" si="7"/>
+        <v>602072.86093499989</v>
+      </c>
+      <c r="F59" s="129">
+        <f t="shared" si="8"/>
+        <v>52994.989064999994</v>
+      </c>
+      <c r="G59" s="107">
+        <f t="shared" si="9"/>
+        <v>655067.85</v>
+      </c>
+      <c r="H59" s="148">
+        <f t="shared" si="10"/>
+        <v>655067.84999999986</v>
+      </c>
+      <c r="I59" s="161">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="C58" s="97"/>
-      <c r="D58" s="111">
+      <c r="B60" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="97"/>
+      <c r="D60" s="111">
         <v>1107047.99</v>
       </c>
-      <c r="E58" s="141">
+      <c r="E60" s="141">
         <f t="shared" si="7"/>
         <v>1017487.8076089999</v>
       </c>
-      <c r="F58" s="129">
+      <c r="F60" s="129">
         <f t="shared" si="8"/>
         <v>89560.182390999995</v>
       </c>
-      <c r="G58" s="107">
+      <c r="G60" s="107">
         <f t="shared" si="9"/>
         <v>1107047.99</v>
       </c>
-      <c r="H58" s="148">
+      <c r="H60" s="148">
         <f t="shared" si="10"/>
         <v>1107047.99</v>
       </c>
-      <c r="I58" s="161">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="205" t="s">
-        <v>167</v>
-      </c>
-      <c r="B59" s="206"/>
-      <c r="C59" s="207"/>
-      <c r="D59" s="111">
-        <v>51000</v>
-      </c>
-      <c r="E59" s="141">
-        <f t="shared" ref="E59" si="13">D59</f>
-        <v>51000</v>
-      </c>
-      <c r="F59" s="129"/>
-      <c r="G59" s="107">
-        <f t="shared" si="9"/>
-        <v>51000</v>
-      </c>
-      <c r="H59" s="148">
-        <f t="shared" si="10"/>
-        <v>51000</v>
-      </c>
-      <c r="I59" s="161">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="179" t="s">
-        <v>165</v>
-      </c>
-      <c r="B60" s="97"/>
-      <c r="C60" s="97"/>
-      <c r="D60" s="111">
-        <v>400000</v>
-      </c>
-      <c r="E60" s="141">
-        <f t="shared" ref="E60:E63" si="14">D60*91.91%</f>
-        <v>367639.99999999994</v>
-      </c>
-      <c r="F60" s="129">
-        <f t="shared" ref="F60:F63" si="15">D60*8.09%</f>
-        <v>32360</v>
-      </c>
-      <c r="G60" s="107">
-        <f t="shared" si="9"/>
-        <v>400000</v>
-      </c>
-      <c r="H60" s="148">
-        <f t="shared" si="10"/>
-        <v>399999.99999999994</v>
-      </c>
       <c r="I60" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -3054,845 +3032,967 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M60" s="172" t="s">
-        <v>137</v>
-      </c>
-      <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="173">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B61" s="97"/>
-      <c r="C61" s="97"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61" s="218" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="219"/>
+      <c r="C61" s="220"/>
       <c r="D61" s="111">
-        <v>47279.57</v>
+        <v>51000</v>
       </c>
       <c r="E61" s="141">
-        <f t="shared" ref="E61:E62" si="16">D61</f>
-        <v>47279.57</v>
+        <f t="shared" ref="E61" si="13">D61</f>
+        <v>51000</v>
       </c>
       <c r="F61" s="129"/>
       <c r="G61" s="107">
         <f t="shared" si="9"/>
-        <v>47279.57</v>
+        <v>51000</v>
       </c>
       <c r="H61" s="148">
         <f t="shared" si="10"/>
-        <v>47279.57</v>
-      </c>
-      <c r="I61" s="161"/>
-      <c r="J61" s="161"/>
-    </row>
-    <row r="62" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+        <v>51000</v>
+      </c>
+      <c r="I61" s="161">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62" s="179" t="s">
+        <v>175</v>
+      </c>
+      <c r="B62" s="97"/>
+      <c r="C62" s="97"/>
+      <c r="D62" s="173">
+        <v>400000</v>
+      </c>
+      <c r="E62" s="141">
+        <f t="shared" ref="E62:E67" si="14">D62*91.91%</f>
+        <v>367639.99999999994</v>
+      </c>
+      <c r="F62" s="129">
+        <f t="shared" ref="F62:F67" si="15">D62*8.09%</f>
+        <v>32360</v>
+      </c>
+      <c r="G62" s="107">
+        <f t="shared" si="9"/>
+        <v>400000</v>
+      </c>
+      <c r="H62" s="148">
+        <f t="shared" si="10"/>
+        <v>399999.99999999994</v>
+      </c>
+      <c r="I62" s="161">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="172" t="s">
+        <v>137</v>
+      </c>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="173">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63" s="179" t="s">
+        <v>174</v>
+      </c>
+      <c r="B63" s="97"/>
+      <c r="C63" s="97"/>
+      <c r="D63" s="173">
+        <v>77541.55</v>
+      </c>
+      <c r="E63" s="141">
+        <f t="shared" si="14"/>
+        <v>71268.438605000003</v>
+      </c>
+      <c r="F63" s="129">
+        <f t="shared" si="15"/>
+        <v>6273.1113949999999</v>
+      </c>
+      <c r="G63" s="107">
+        <f t="shared" si="9"/>
+        <v>77541.55</v>
+      </c>
+      <c r="H63" s="148">
+        <f t="shared" si="10"/>
+        <v>77541.55</v>
+      </c>
+      <c r="I63" s="161">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="258"/>
+      <c r="N63" s="259"/>
+      <c r="O63" s="259"/>
+      <c r="P63" s="260"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B64" s="97"/>
+      <c r="C64" s="97"/>
+      <c r="D64" s="173">
+        <v>185000</v>
+      </c>
+      <c r="E64" s="141">
+        <f t="shared" ref="E64:E66" si="16">D64</f>
+        <v>185000</v>
+      </c>
+      <c r="F64" s="129"/>
+      <c r="G64" s="107">
+        <f t="shared" si="9"/>
+        <v>185000</v>
+      </c>
+      <c r="H64" s="148">
+        <f t="shared" si="10"/>
+        <v>185000</v>
+      </c>
+      <c r="I64" s="161"/>
+      <c r="J64" s="161"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="172" t="s">
+        <v>173</v>
+      </c>
+      <c r="B65" s="97"/>
+      <c r="C65" s="97"/>
+      <c r="D65" s="173">
+        <v>85795.1</v>
+      </c>
+      <c r="E65" s="141"/>
+      <c r="F65" s="129"/>
+      <c r="G65" s="107">
+        <f t="shared" si="9"/>
+        <v>85795.1</v>
+      </c>
+      <c r="H65" s="148"/>
+      <c r="I65" s="161"/>
+      <c r="J65" s="161"/>
+    </row>
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="111">
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="111">
         <v>88294</v>
       </c>
-      <c r="E62" s="141">
+      <c r="E66" s="141">
         <f t="shared" si="16"/>
         <v>88294</v>
       </c>
-      <c r="F62" s="129"/>
-      <c r="G62" s="107">
+      <c r="F66" s="129"/>
+      <c r="G66" s="107">
         <f t="shared" si="9"/>
         <v>88294</v>
       </c>
-      <c r="H62" s="148">
+      <c r="H66" s="148">
         <f t="shared" si="10"/>
         <v>88294</v>
       </c>
-      <c r="I62" s="161">
+      <c r="I66" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J62" s="161">
+      <c r="J66" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="119" t="s">
-        <v>156</v>
-      </c>
-      <c r="B63" s="112"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="111">
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="119" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" s="112"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="111">
         <v>90143.44</v>
       </c>
-      <c r="E63" s="141">
+      <c r="E67" s="141">
         <f t="shared" si="14"/>
         <v>82850.835703999997</v>
       </c>
-      <c r="F63" s="129">
+      <c r="F67" s="129">
         <f t="shared" si="15"/>
         <v>7292.6042960000004</v>
       </c>
-      <c r="G63" s="107">
+      <c r="G67" s="107">
         <f t="shared" si="9"/>
         <v>90143.44</v>
       </c>
-      <c r="H63" s="148">
+      <c r="H67" s="148">
         <f t="shared" si="10"/>
         <v>90143.44</v>
       </c>
-      <c r="I63" s="161"/>
-      <c r="J63" s="161"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="94" t="s">
+      <c r="I67" s="161"/>
+      <c r="J67" s="161"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="95"/>
-      <c r="C64" s="95"/>
-      <c r="D64" s="106">
-        <f>SUM(D51:D63)</f>
-        <v>3939711.16</v>
-      </c>
-      <c r="E64" s="106">
-        <f>SUM(E51:E63)</f>
-        <v>3669332.2289689998</v>
-      </c>
-      <c r="F64" s="106">
-        <f>SUM(F51:F63)</f>
-        <v>270378.93103099999</v>
-      </c>
-      <c r="G64" s="107">
-        <f>E64+F64</f>
-        <v>3939711.1599999997</v>
-      </c>
-      <c r="H64" s="142" t="str">
-        <f>IF(D64=G64, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I64" s="161">
-        <f>D64-G64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="166"/>
-      <c r="E65" s="113"/>
-      <c r="F65" s="7"/>
-      <c r="H65" s="142"/>
-    </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="166"/>
-      <c r="E66" s="112"/>
-      <c r="F66" s="7"/>
-      <c r="H66" s="142"/>
-    </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="166"/>
-      <c r="E67" s="112"/>
-      <c r="F67" s="7"/>
-      <c r="H67" s="142"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="93" t="s">
-        <v>141</v>
-      </c>
-      <c r="B68" s="97"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="111">
-        <v>112680</v>
-      </c>
-      <c r="E68" s="141">
-        <f>D68*91.91%</f>
-        <v>103564.18799999999</v>
-      </c>
-      <c r="F68" s="129">
-        <f>D68*8.09%</f>
-        <v>9115.8119999999999</v>
-      </c>
-      <c r="G68" s="147"/>
-      <c r="H68" s="142"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="95"/>
+      <c r="C68" s="95"/>
+      <c r="D68" s="106">
+        <f>SUM(D51:D67)</f>
+        <v>5122119.24</v>
+      </c>
+      <c r="E68" s="106">
+        <f>SUM(E51:E67)</f>
+        <v>3407774.1028379998</v>
+      </c>
+      <c r="F68" s="106">
+        <f>SUM(F51:F67)</f>
+        <v>235234.07716200003</v>
+      </c>
+      <c r="G68" s="107">
+        <f>E68+F68</f>
+        <v>3643008.1799999997</v>
+      </c>
+      <c r="H68" s="142" t="str">
+        <f>IF(D68=G68, "", "Error")</f>
+        <v>Error</v>
+      </c>
+      <c r="I68" s="161">
+        <f>D68-G68</f>
+        <v>1479111.0600000005</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
-      <c r="D69" s="111"/>
-      <c r="E69" s="150">
-        <f>D69</f>
-        <v>0</v>
-      </c>
+      <c r="D69" s="166"/>
+      <c r="E69" s="113"/>
       <c r="F69" s="7"/>
       <c r="H69" s="142"/>
-      <c r="I69" s="107"/>
-    </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="94" t="s">
-        <v>16</v>
-      </c>
-      <c r="B70" s="94"/>
-      <c r="C70" s="94"/>
-      <c r="D70" s="106">
-        <f>SUM(D68:D69)</f>
-        <v>112680</v>
-      </c>
-      <c r="E70" s="106">
-        <f>SUM(E68:E69)</f>
-        <v>103564.18799999999</v>
-      </c>
-      <c r="F70" s="106">
-        <f>SUM(F68:F69)</f>
-        <v>9115.8119999999999</v>
-      </c>
-      <c r="G70" s="107">
-        <f>E70+F70</f>
-        <v>112680</v>
-      </c>
-      <c r="H70" s="142" t="str">
-        <f>IF(D70=G70, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J70" s="107"/>
-    </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="166"/>
+      <c r="E70" s="112"/>
+      <c r="F70" s="7"/>
+      <c r="H70" s="142"/>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="166"/>
-      <c r="E71" s="113"/>
+      <c r="E71" s="112"/>
       <c r="F71" s="7"/>
       <c r="H71" s="142"/>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="97"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="166"/>
-      <c r="E72" s="112"/>
-      <c r="F72" s="7"/>
+      <c r="D72" s="173">
+        <v>117300</v>
+      </c>
+      <c r="E72" s="141">
+        <f>D72*91.91%</f>
+        <v>107810.43</v>
+      </c>
+      <c r="F72" s="129">
+        <f>D72*8.09%</f>
+        <v>9489.57</v>
+      </c>
+      <c r="G72" s="147"/>
       <c r="H72" s="142"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="93" t="s">
-        <v>13</v>
-      </c>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="166"/>
-      <c r="E73" s="112"/>
+      <c r="D73" s="111"/>
+      <c r="E73" s="150">
+        <f>D73</f>
+        <v>0</v>
+      </c>
       <c r="F73" s="7"/>
       <c r="H73" s="142"/>
-    </row>
-    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="93" t="s">
-        <v>14</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="111">
-        <v>246000</v>
-      </c>
-      <c r="E74" s="141">
-        <f>D74*91.91%</f>
-        <v>226098.59999999998</v>
-      </c>
-      <c r="F74" s="129">
-        <f>D74*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G74" t="s">
-        <v>139</v>
-      </c>
-      <c r="H74" s="142"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="93" t="s">
-        <v>107</v>
-      </c>
+      <c r="I73" s="107"/>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" s="94"/>
+      <c r="C74" s="94"/>
+      <c r="D74" s="106">
+        <f>SUM(D72:D73)</f>
+        <v>117300</v>
+      </c>
+      <c r="E74" s="106">
+        <f>SUM(E72:E73)</f>
+        <v>107810.43</v>
+      </c>
+      <c r="F74" s="106">
+        <f>SUM(F72:F73)</f>
+        <v>9489.57</v>
+      </c>
+      <c r="G74" s="107">
+        <f>E74+F74</f>
+        <v>117300</v>
+      </c>
+      <c r="H74" s="142" t="str">
+        <f>IF(D74=G74, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J74" s="107"/>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="111">
-        <v>35000</v>
-      </c>
-      <c r="E75" s="141">
-        <f>D75*91.91%</f>
-        <v>32168.499999999996</v>
-      </c>
-      <c r="F75" s="129">
-        <f>D75*8.09%</f>
-        <v>2831.5</v>
-      </c>
+      <c r="D75" s="166"/>
+      <c r="E75" s="113"/>
+      <c r="F75" s="7"/>
       <c r="H75" s="142"/>
-      <c r="J75" s="111"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="166"/>
-      <c r="E76" s="114"/>
+      <c r="E76" s="112"/>
       <c r="F76" s="7"/>
       <c r="H76" s="142"/>
-      <c r="J76" s="107"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77" s="94"/>
-      <c r="C77" s="94"/>
-      <c r="D77" s="106">
-        <f>SUM(D74:D76)</f>
-        <v>281000</v>
-      </c>
-      <c r="E77" s="106">
-        <f>SUM(E74:E76)</f>
-        <v>258267.09999999998</v>
-      </c>
-      <c r="F77" s="106">
-        <f>SUM(F74:F76)</f>
-        <v>22732.9</v>
-      </c>
-      <c r="G77" s="107">
-        <f>E77+F77</f>
-        <v>281000</v>
-      </c>
-      <c r="H77" s="142" t="str">
-        <f>IF(D77=G77, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J77" s="107"/>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="166"/>
+      <c r="E77" s="112"/>
+      <c r="F77" s="7"/>
+      <c r="H77" s="142"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="93" t="s">
-        <v>100</v>
-      </c>
-      <c r="B78" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="C78" s="7"/>
-      <c r="D78" s="111"/>
-      <c r="E78" s="115"/>
-      <c r="F78" s="7"/>
+      <c r="D78" s="111">
+        <v>246000</v>
+      </c>
+      <c r="E78" s="141">
+        <f>D78*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F78" s="129">
+        <f>D78*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G78" t="s">
+        <v>139</v>
+      </c>
       <c r="H78" s="142"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="93" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="111">
-        <f>155582.25+151.2+3552+9324+348.88+1800</f>
-        <v>170758.33000000002</v>
+        <v>35000</v>
       </c>
       <c r="E79" s="141">
         <f>D79*91.91%</f>
-        <v>156943.981103</v>
+        <v>32168.499999999996</v>
       </c>
       <c r="F79" s="129">
         <f>D79*8.09%</f>
-        <v>13814.348897000002</v>
+        <v>2831.5</v>
       </c>
       <c r="H79" s="142"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="93" t="s">
-        <v>102</v>
-      </c>
+      <c r="J79" s="111"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="7"/>
       <c r="B80" s="7"/>
-      <c r="C80" s="120"/>
-      <c r="D80" s="111">
-        <v>44400</v>
-      </c>
-      <c r="E80" s="141">
-        <f>D80*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F80" s="129">
-        <f>D80*8.09%</f>
-        <v>3591.96</v>
-      </c>
+      <c r="C80" s="7"/>
+      <c r="D80" s="166"/>
+      <c r="E80" s="114"/>
+      <c r="F80" s="7"/>
       <c r="H80" s="142"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J80" s="107"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="94" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="B81" s="94"/>
       <c r="C81" s="94"/>
-      <c r="D81" s="145">
-        <f>SUM(D79:D80)</f>
-        <v>215158.33000000002</v>
-      </c>
-      <c r="E81" s="139">
-        <f t="shared" ref="E81:F81" si="17">SUM(E79:E80)</f>
-        <v>197752.02110299998</v>
-      </c>
-      <c r="F81" s="139">
-        <f t="shared" si="17"/>
-        <v>17406.308897000003</v>
+      <c r="D81" s="106">
+        <f>SUM(D78:D80)</f>
+        <v>281000</v>
+      </c>
+      <c r="E81" s="106">
+        <f>SUM(E78:E80)</f>
+        <v>258267.09999999998</v>
+      </c>
+      <c r="F81" s="106">
+        <f>SUM(F78:F80)</f>
+        <v>22732.9</v>
       </c>
       <c r="G81" s="107">
         <f>E81+F81</f>
-        <v>215158.33</v>
+        <v>281000</v>
       </c>
       <c r="H81" s="142" t="str">
         <f>IF(D81=G81, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="7"/>
+      <c r="J81" s="107"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="93" t="s">
+        <v>100</v>
+      </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="167"/>
-      <c r="E82" s="11"/>
+      <c r="D82" s="111"/>
+      <c r="E82" s="115"/>
       <c r="F82" s="7"/>
       <c r="H82" s="142"/>
     </row>
-    <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="98" t="s">
-        <v>133</v>
-      </c>
-      <c r="B83" s="98"/>
-      <c r="C83" s="98"/>
-      <c r="D83" s="168">
-        <f>7000000-6426943.64</f>
-        <v>573056.36000000034</v>
-      </c>
-      <c r="E83" s="116">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="111">
+        <f>155582.25+151.2+3552+9324+348.88+1800</f>
+        <v>170758.33000000002</v>
+      </c>
+      <c r="E83" s="141">
         <f>D83*91.91%</f>
-        <v>526696.10047600023</v>
-      </c>
-      <c r="F83" s="131">
+        <v>156943.981103</v>
+      </c>
+      <c r="F83" s="129">
         <f>D83*8.09%</f>
-        <v>46360.25952400003</v>
-      </c>
-      <c r="G83" s="107">
-        <f>E83+F83</f>
-        <v>573056.36000000022</v>
-      </c>
-      <c r="H83" s="142" t="str">
-        <f>IF(D83=G83, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
-      <c r="D84" s="165"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="144"/>
+        <v>13814.348897000002</v>
+      </c>
+      <c r="H83" s="142"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="7"/>
+      <c r="C84" s="120"/>
+      <c r="D84" s="111">
+        <v>44400</v>
+      </c>
+      <c r="E84" s="141">
+        <f>D84*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F84" s="129">
+        <f>D84*8.09%</f>
+        <v>3591.96</v>
+      </c>
       <c r="H84" s="142"/>
     </row>
-    <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="59"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="169">
-        <f>SUM(D83+D81+D77+D70+D64+D49+D32+D27+D44)</f>
-        <v>7000000.0000000009</v>
-      </c>
-      <c r="E85" s="140">
-        <f>SUM(E83+E81+E77+E70+E64+E49+E32+E27+E44)</f>
-        <v>6482043.7018129993</v>
-      </c>
-      <c r="F85" s="140">
-        <f>SUM(F83+F81+F77+F70+F64+F49+F32+F27+F44)</f>
-        <v>517956.29818700004</v>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="94"/>
+      <c r="C85" s="94"/>
+      <c r="D85" s="145">
+        <f>SUM(D83:D84)</f>
+        <v>215158.33000000002</v>
+      </c>
+      <c r="E85" s="139">
+        <f t="shared" ref="E85:F85" si="17">SUM(E83:E84)</f>
+        <v>197752.02110299998</v>
+      </c>
+      <c r="F85" s="139">
+        <f t="shared" si="17"/>
+        <v>17406.308897000003</v>
       </c>
       <c r="G85" s="107">
         <f>E85+F85</f>
-        <v>6999999.9999999991</v>
+        <v>215158.33</v>
       </c>
       <c r="H85" s="142" t="str">
         <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
-      <c r="I85" s="161">
-        <f>D85-G85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D86" s="165"/>
-      <c r="E86" s="107"/>
-    </row>
-    <row r="87" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="175" t="s">
+    </row>
+    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="167"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="7"/>
+      <c r="H86" s="142"/>
+    </row>
+    <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="98" t="s">
+        <v>133</v>
+      </c>
+      <c r="B87" s="98"/>
+      <c r="C87" s="98"/>
+      <c r="D87" s="168">
+        <f>7000000-6426943.64</f>
+        <v>573056.36000000034</v>
+      </c>
+      <c r="E87" s="116">
+        <f>D87*91.91%</f>
+        <v>526696.10047600023</v>
+      </c>
+      <c r="F87" s="131">
+        <f>D87*8.09%</f>
+        <v>46360.25952400003</v>
+      </c>
+      <c r="G87" s="107">
+        <f>E87+F87</f>
+        <v>573056.36000000022</v>
+      </c>
+      <c r="H87" s="142" t="str">
+        <f>IF(D87=G87, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="1"/>
+      <c r="D88" s="165"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="144"/>
+      <c r="H88" s="142"/>
+    </row>
+    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="59"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="169">
+        <f>SUM(D87+D85+D81+D74+D68+D49+D32+D27+D44)</f>
+        <v>8184667.3900000006</v>
+      </c>
+      <c r="E89" s="140">
+        <f>SUM(E87+E85+E81+E74+E68+E49+E32+E27+E44)</f>
+        <v>6222562.1075030006</v>
+      </c>
+      <c r="F89" s="140">
+        <f>SUM(F87+F85+F81+F74+F68+F49+F32+F27+F44)</f>
+        <v>482994.22249700007</v>
+      </c>
+      <c r="G89" s="107">
+        <f>E89+F89</f>
+        <v>6705556.330000001</v>
+      </c>
+      <c r="H89" s="142" t="str">
+        <f>IF(D89=G89, "", "Error")</f>
+        <v>Error</v>
+      </c>
+      <c r="I89" s="161">
+        <f>D89-G89</f>
+        <v>1479111.0599999996</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D90" s="165"/>
+      <c r="E90" s="107"/>
+    </row>
+    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="175" t="s">
         <v>152</v>
       </c>
-      <c r="B87" s="136"/>
-      <c r="C87" s="136"/>
-      <c r="E87" s="107"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="C88" s="134"/>
-      <c r="E88" s="107"/>
-    </row>
-    <row r="89" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="1"/>
-      <c r="C89" s="134"/>
-      <c r="E89" s="107"/>
-    </row>
-    <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="137" t="s">
+      <c r="B91" s="136"/>
+      <c r="C91" s="136"/>
+      <c r="E91" s="107"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="C92" s="134"/>
+      <c r="E92" s="107"/>
+    </row>
+    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="1"/>
+      <c r="C93" s="134"/>
+      <c r="E93" s="107"/>
+    </row>
+    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="B90" s="138"/>
-      <c r="C90" s="135">
-        <f>SUM(C88:C89)</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="107"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E91" s="107"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E92" s="132"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="203" t="s">
+      <c r="B94" s="138"/>
+      <c r="C94" s="135">
+        <f>SUM(C92:C93)</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="107"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E95" s="107"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E96" s="132"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="B93" s="204"/>
-      <c r="C93" s="204"/>
-      <c r="D93" s="204"/>
-      <c r="E93" s="156" t="s">
+      <c r="B97" s="217"/>
+      <c r="C97" s="217"/>
+      <c r="D97" s="217"/>
+      <c r="E97" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="F93" s="157" t="s">
+      <c r="F97" s="157" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="200" t="s">
-        <v>170</v>
-      </c>
-      <c r="B94" s="201"/>
-      <c r="C94" s="202"/>
-      <c r="D94" s="111">
+    <row r="98" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="213" t="s">
+        <v>164</v>
+      </c>
+      <c r="B98" s="214"/>
+      <c r="C98" s="215"/>
+      <c r="D98" s="111">
         <v>2900000</v>
       </c>
-      <c r="E94" s="141">
-        <f t="shared" ref="E94:E95" si="18">D94*91.91%</f>
+      <c r="E98" s="141">
+        <f t="shared" ref="E98:E99" si="18">D98*91.91%</f>
         <v>2665389.9999999995</v>
       </c>
-      <c r="F94" s="129">
-        <f t="shared" ref="F94:F95" si="19">D94*8.09%</f>
+      <c r="F98" s="129">
+        <f t="shared" ref="F98:F99" si="19">D98*8.09%</f>
         <v>234610</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="208"/>
-      <c r="B95" s="209"/>
-      <c r="C95" s="210"/>
-      <c r="D95" s="111"/>
-      <c r="E95" s="141">
+    <row r="99" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="221"/>
+      <c r="B99" s="222"/>
+      <c r="C99" s="223"/>
+      <c r="D99" s="111"/>
+      <c r="E99" s="141">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="F95" s="129">
+      <c r="F99" s="129">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="197" t="s">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="210" t="s">
         <v>29</v>
       </c>
-      <c r="B96" s="198"/>
-      <c r="C96" s="199"/>
-      <c r="D96" s="155">
-        <f>SUM(D94:D95)</f>
+      <c r="B100" s="211"/>
+      <c r="C100" s="212"/>
+      <c r="D100" s="155">
+        <f>SUM(D98:D99)</f>
         <v>2900000</v>
       </c>
-      <c r="E96" s="155">
-        <f>SUM(E94:E95)</f>
+      <c r="E100" s="155">
+        <f>SUM(E98:E99)</f>
         <v>2665389.9999999995</v>
       </c>
-      <c r="F96" s="155">
-        <f>SUM(F94:F95)</f>
+      <c r="F100" s="155">
+        <f>SUM(F98:F99)</f>
         <v>234610</v>
       </c>
-      <c r="H96" s="107">
-        <f>E96+F96</f>
+      <c r="H100" s="107">
+        <f>E100+F100</f>
         <v>2899999.9999999995</v>
       </c>
-      <c r="I96" s="142" t="str">
-        <f>IF(D96=H96, "", "Error")</f>
+      <c r="I100" s="142" t="str">
+        <f>IF(D100=H100, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E98" s="107"/>
-    </row>
-    <row r="99" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="101" t="s">
+    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E102" s="107"/>
+    </row>
+    <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="B99" s="102">
-        <f>D85</f>
-        <v>7000000.0000000009</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="103" t="s">
+      <c r="B103" s="102">
+        <f>D89</f>
+        <v>8184667.3900000006</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="B100" s="104">
-        <f>D85-D83</f>
-        <v>6426943.6400000006</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D101" s="187"/>
-      <c r="E101" s="187"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="73" t="s">
+      <c r="B104" s="104">
+        <f>D89-D87</f>
+        <v>7611611.0300000003</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D105" s="200"/>
+      <c r="E105" s="200"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="B102" s="74"/>
-      <c r="C102" s="75"/>
-      <c r="D102" s="187"/>
-      <c r="E102" s="187"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="B106" s="74"/>
+      <c r="C106" s="75"/>
+      <c r="D106" s="200"/>
+      <c r="E106" s="200"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B107" s="10">
         <v>3617497.2979896166</v>
       </c>
-      <c r="C103" s="77"/>
-      <c r="D103" s="187"/>
-      <c r="E103" s="187"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="78" t="s">
+      <c r="C107" s="77"/>
+      <c r="D107" s="200"/>
+      <c r="E107" s="200"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="B104" s="91">
+      <c r="B108" s="91">
         <f>PRORRATEO!G52</f>
         <v>6941937.3369510006</v>
       </c>
-      <c r="C104" s="77" t="s">
+      <c r="C108" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="D104" s="187"/>
-      <c r="E104" s="187"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="78" t="s">
+      <c r="D108" s="200"/>
+      <c r="E108" s="200"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="78" t="s">
         <v>115</v>
       </c>
-      <c r="B105" s="158">
-        <f>-B100</f>
-        <v>-6426943.6400000006</v>
-      </c>
-      <c r="C105" s="75"/>
-      <c r="D105" s="187"/>
-      <c r="E105" s="187"/>
-      <c r="G105" s="111"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="78" t="s">
+      <c r="B109" s="158">
+        <f>-B104</f>
+        <v>-7611611.0300000003</v>
+      </c>
+      <c r="C109" s="75"/>
+      <c r="D109" s="200"/>
+      <c r="E109" s="200"/>
+      <c r="G109" s="111"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="158">
-        <f>-D96</f>
+      <c r="B110" s="158">
+        <f>-D100</f>
         <v>-2900000</v>
       </c>
-      <c r="C106" s="75"/>
-      <c r="D106" s="187"/>
-      <c r="E106" s="187"/>
-      <c r="G106" s="121"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="78" t="s">
-        <v>171</v>
-      </c>
-      <c r="B107" s="158">
+      <c r="C110" s="75"/>
+      <c r="D110" s="200"/>
+      <c r="E110" s="200"/>
+      <c r="G110" s="121"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="78" t="s">
+        <v>165</v>
+      </c>
+      <c r="B111" s="158">
         <f>-77229-250000</f>
         <v>-327229</v>
       </c>
-      <c r="C107" s="75"/>
-      <c r="D107" s="182"/>
-      <c r="E107" s="182"/>
-      <c r="G107" s="121"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="78" t="s">
-        <v>172</v>
-      </c>
-      <c r="B108" s="158">
+      <c r="C111" s="75"/>
+      <c r="D111" s="182"/>
+      <c r="E111" s="182"/>
+      <c r="G111" s="121"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="78" t="s">
+        <v>166</v>
+      </c>
+      <c r="B112" s="158">
         <f>-19000*2</f>
         <v>-38000</v>
       </c>
-      <c r="C108" s="75"/>
-      <c r="D108" s="182"/>
-      <c r="E108" s="182"/>
-      <c r="G108" s="121"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="78" t="s">
+      <c r="C112" s="75"/>
+      <c r="D112" s="182"/>
+      <c r="E112" s="182"/>
+      <c r="G112" s="121"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A113" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B109" s="158">
-        <f>-B116</f>
+      <c r="B113" s="158">
+        <f>-B120</f>
         <v>-60000</v>
       </c>
-      <c r="C109" s="79"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="78" t="s">
+      <c r="C113" s="79"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A114" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="B110" s="92">
-        <f>-C90</f>
-        <v>0</v>
-      </c>
-      <c r="C110" s="79"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="78"/>
-      <c r="B111" s="74"/>
-      <c r="C111" s="143"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="76" t="s">
+      <c r="B114" s="92">
+        <f>-C94</f>
+        <v>0</v>
+      </c>
+      <c r="C114" s="79"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A115" s="78"/>
+      <c r="B115" s="74"/>
+      <c r="C115" s="143"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A116" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="B112" s="80">
-        <f>SUM(B103:B111)</f>
-        <v>807261.99494061619</v>
-      </c>
-      <c r="C112" s="143"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="79"/>
-      <c r="C113" s="75"/>
-      <c r="D113" s="82"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C114" s="75"/>
-      <c r="D114" s="107"/>
-      <c r="E114" s="161"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="73" t="s">
+      <c r="B116" s="80">
+        <f>SUM(B107:B115)</f>
+        <v>-377405.39505938347</v>
+      </c>
+      <c r="C116" s="143"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A117" s="79"/>
+      <c r="C117" s="75"/>
+      <c r="D117" s="82"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C118" s="75"/>
+      <c r="D118" s="107"/>
+      <c r="E118" s="161"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A119" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="184">
+      <c r="B119" s="184">
         <v>-272694.54000000004</v>
       </c>
-      <c r="C115" s="81"/>
-      <c r="D115" s="161"/>
-      <c r="E115" s="161"/>
-      <c r="F115" s="161"/>
-    </row>
-    <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="B116" s="92">
+      <c r="C119" s="81"/>
+      <c r="D119" s="161"/>
+      <c r="E119" s="161"/>
+      <c r="F119" s="161"/>
+    </row>
+    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="B120" s="92">
         <v>60000</v>
       </c>
-      <c r="C116" s="81"/>
-      <c r="D116" s="161"/>
-      <c r="E116" s="171"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="76"/>
-      <c r="B117" s="158"/>
-      <c r="C117" s="81"/>
-      <c r="E117" s="107"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="76"/>
-      <c r="B118" s="158"/>
-      <c r="C118" s="81"/>
-      <c r="E118" s="107"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="99" t="s">
+      <c r="C120" s="81"/>
+      <c r="D120" s="161"/>
+      <c r="E120" s="171"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A121" s="76"/>
+      <c r="B121" s="158"/>
+      <c r="C121" s="81"/>
+      <c r="E121" s="107"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A122" s="76"/>
+      <c r="B122" s="158"/>
+      <c r="C122" s="81"/>
+      <c r="E122" s="107"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A123" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B119" s="100">
-        <f>SUM(B115:B118)</f>
+      <c r="B123" s="100">
+        <f>SUM(B119:B122)</f>
         <v>-212694.54000000004</v>
       </c>
-      <c r="C119" s="81"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C120" s="82"/>
-      <c r="D120" s="161"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B121" s="79"/>
-      <c r="C121" s="75"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N123" s="11"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B126" s="186"/>
-      <c r="C126" s="186"/>
-      <c r="D126" s="186"/>
-      <c r="E126" s="186"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B127" s="186"/>
-      <c r="C127" s="186"/>
-      <c r="D127" s="186"/>
-      <c r="E127" s="186"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B128" s="186"/>
-      <c r="C128" s="186"/>
-      <c r="D128" s="186"/>
-      <c r="E128" s="186"/>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="186"/>
-      <c r="C129" s="186"/>
-      <c r="D129" s="186"/>
-      <c r="E129" s="186"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="186"/>
-      <c r="C130" s="186"/>
-      <c r="D130" s="186"/>
-      <c r="E130" s="186"/>
+      <c r="C123" s="81"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C124" s="82"/>
+      <c r="D124" s="161"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B125" s="79"/>
+      <c r="C125" s="75"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N127" s="11"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B130" s="199"/>
+      <c r="C130" s="199"/>
+      <c r="D130" s="199"/>
+      <c r="E130" s="199"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B131" s="199"/>
+      <c r="C131" s="199"/>
+      <c r="D131" s="199"/>
+      <c r="E131" s="199"/>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B132" s="199"/>
+      <c r="C132" s="199"/>
+      <c r="D132" s="199"/>
+      <c r="E132" s="199"/>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B133" s="199"/>
+      <c r="C133" s="199"/>
+      <c r="D133" s="199"/>
+      <c r="E133" s="199"/>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B134" s="199"/>
+      <c r="C134" s="199"/>
+      <c r="D134" s="199"/>
+      <c r="E134" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B126:E130"/>
-    <mergeCell ref="D101:E106"/>
+    <mergeCell ref="B130:E134"/>
+    <mergeCell ref="D105:E110"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A93:D93"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A99:C99"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3903,185 +4003,185 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
-    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="237" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="238"/>
-      <c r="F1" s="238"/>
-      <c r="G1" s="238"/>
-      <c r="H1" s="238"/>
-      <c r="I1" s="238"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="245" t="s">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="238" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="240"/>
+      <c r="K1" s="188" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="246">
-        <f>RESUMEN!D85</f>
-        <v>7000000.0000000009</v>
-      </c>
-      <c r="M1" s="247"/>
-      <c r="N1" s="248"/>
+      <c r="L1" s="227">
+        <f>RESUMEN!D89</f>
+        <v>8184667.3900000006</v>
+      </c>
+      <c r="M1" s="228"/>
+      <c r="N1" s="189"/>
       <c r="O1" s="130">
         <f>L1*8.09%</f>
-        <v>566300.00000000012</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="240"/>
-      <c r="B2" s="241"/>
-      <c r="C2" s="241"/>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="241"/>
-      <c r="I2" s="241"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="249" t="s">
+        <v>662139.59185100009</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="241"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="242"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="190" t="s">
         <v>125</v>
       </c>
-      <c r="L2" s="250"/>
-      <c r="M2" s="251">
+      <c r="L2" s="8"/>
+      <c r="M2" s="191">
         <v>7000000</v>
       </c>
-      <c r="N2" s="252"/>
+      <c r="N2" s="192"/>
       <c r="O2" s="130">
         <f>O1-K7-553-50-86-8</f>
-        <v>47646.70181300008</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="240"/>
-      <c r="B3" s="241"/>
-      <c r="C3" s="241"/>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="241"/>
-      <c r="I3" s="241"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="249" t="s">
+        <v>143486.29366400006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="241"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="242"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="190" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="250"/>
-      <c r="M3" s="253">
-        <f>RESUMEN!D96</f>
+      <c r="L3" s="8"/>
+      <c r="M3" s="193">
+        <f>RESUMEN!D100</f>
         <v>2900000</v>
       </c>
-      <c r="N3" s="254"/>
+      <c r="N3" s="194"/>
       <c r="O3" s="72"/>
     </row>
-    <row r="4" spans="1:16" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="243"/>
-      <c r="B4" s="236"/>
-      <c r="C4" s="236"/>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="255" t="s">
+    <row r="4" spans="1:16" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="244"/>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="195" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="256"/>
-      <c r="M4" s="257">
+      <c r="L4" s="196"/>
+      <c r="M4" s="197">
         <f>O4</f>
         <v>966666.66666666663</v>
       </c>
-      <c r="N4" s="258"/>
+      <c r="N4" s="198"/>
       <c r="O4" s="130">
         <f>M3/3</f>
         <v>966666.66666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="211" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="213" t="s">
+      <c r="B5" s="247" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="211" t="s">
+      <c r="C5" s="224" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="215" t="s">
+      <c r="D5" s="236" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="211" t="s">
+      <c r="E5" s="224" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="211" t="s">
+      <c r="F5" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="211" t="s">
+      <c r="G5" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="220" t="s">
+      <c r="H5" s="231" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="215" t="s">
+      <c r="I5" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="218" t="s">
+      <c r="J5" s="229" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="218" t="s">
+      <c r="K5" s="229" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="223" t="s">
+      <c r="L5" s="234" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="218" t="s">
+      <c r="M5" s="229" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="218" t="s">
+      <c r="N5" s="229" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="212"/>
-      <c r="B6" s="214"/>
-      <c r="C6" s="212"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="212"/>
-      <c r="G6" s="212"/>
-      <c r="H6" s="221"/>
-      <c r="I6" s="225"/>
-      <c r="J6" s="219"/>
-      <c r="K6" s="222"/>
-      <c r="L6" s="224"/>
-      <c r="M6" s="222"/>
-      <c r="N6" s="219"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="225"/>
+      <c r="B6" s="248"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="249"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="225"/>
+      <c r="G6" s="225"/>
+      <c r="H6" s="232"/>
+      <c r="I6" s="237"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="233"/>
+      <c r="L6" s="235"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="230"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4126,7 +4226,7 @@
         <v>631929.20941155334</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4161,7 +4261,7 @@
         <f>M$2*E8 /100</f>
         <v>154700</v>
       </c>
-      <c r="L8" s="234"/>
+      <c r="L8" s="186"/>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
         <v>175269.60349784917</v>
@@ -4171,7 +4271,7 @@
         <v>185785.77970772012</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4207,7 +4307,7 @@
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>294700</v>
       </c>
-      <c r="L9" s="234">
+      <c r="L9" s="186">
         <v>10000</v>
       </c>
       <c r="M9" s="6">
@@ -4219,7 +4319,7 @@
         <v>366120.75237298576</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4255,7 +4355,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L10" s="234"/>
+      <c r="L10" s="186"/>
       <c r="M10" s="6">
         <f t="shared" si="4"/>
         <v>226253.33333333334</v>
@@ -4265,7 +4365,7 @@
         <v>239828.53333333335</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4301,7 +4401,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L11" s="234"/>
+      <c r="L11" s="186"/>
       <c r="M11" s="6">
         <f t="shared" si="4"/>
         <v>273256.66666666669</v>
@@ -4312,7 +4412,7 @@
       </c>
       <c r="P11" s="107"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4348,7 +4448,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L12" s="234"/>
+      <c r="L12" s="186"/>
       <c r="M12" s="6">
         <f t="shared" si="4"/>
         <v>226253.33333333334</v>
@@ -4358,7 +4458,7 @@
         <v>239828.53333333335</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4394,7 +4494,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L13" s="234"/>
+      <c r="L13" s="186"/>
       <c r="M13" s="6">
         <f t="shared" si="4"/>
         <v>350798.03408590844</v>
@@ -4404,7 +4504,7 @@
         <v>371845.91613106296</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4439,7 +4539,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L14" s="234">
+      <c r="L14" s="186">
         <v>10000</v>
       </c>
       <c r="M14" s="6">
@@ -4451,7 +4551,7 @@
         <v>263885.02133333334</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4487,7 +4587,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L15" s="234"/>
+      <c r="L15" s="186"/>
       <c r="M15" s="6">
         <f t="shared" si="4"/>
         <v>273256.53766320064</v>
@@ -4497,7 +4597,7 @@
         <v>289651.92992299265</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4533,7 +4633,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L16" s="234"/>
+      <c r="L16" s="186"/>
       <c r="M16" s="6">
         <f t="shared" si="4"/>
         <v>211368.25128333337</v>
@@ -4543,7 +4643,7 @@
         <v>224050.34636033338</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4579,7 +4679,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L17" s="234"/>
+      <c r="L17" s="186"/>
       <c r="M17" s="6">
         <f t="shared" si="4"/>
         <v>273256.64067778143</v>
@@ -4589,7 +4689,7 @@
         <v>289652.03911844833</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -4625,7 +4725,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L18" s="234"/>
+      <c r="L18" s="186"/>
       <c r="M18" s="6">
         <f t="shared" si="4"/>
         <v>219422.76046658467</v>
@@ -4635,7 +4735,7 @@
         <v>232588.12609457975</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -4671,7 +4771,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L19" s="234"/>
+      <c r="L19" s="186"/>
       <c r="M19" s="6">
         <f t="shared" si="4"/>
         <v>273257.15298183472</v>
@@ -4681,7 +4781,7 @@
         <v>289652.58216074482</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -4717,7 +4817,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L20" s="234"/>
+      <c r="L20" s="186"/>
       <c r="M20" s="6">
         <f t="shared" si="4"/>
         <v>226252.98919040806</v>
@@ -4727,7 +4827,7 @@
         <v>239828.16854183254</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4763,7 +4863,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L21" s="234"/>
+      <c r="L21" s="186"/>
       <c r="M21" s="6">
         <f t="shared" si="4"/>
         <v>273256.55530846259</v>
@@ -4773,7 +4873,7 @@
         <v>289651.94862697035</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -4809,7 +4909,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L22" s="234"/>
+      <c r="L22" s="186"/>
       <c r="M22" s="6">
         <f t="shared" si="4"/>
         <v>226253.33333333334</v>
@@ -4819,7 +4919,7 @@
         <v>239828.53333333335</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -4855,7 +4955,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L23" s="234"/>
+      <c r="L23" s="186"/>
       <c r="M23" s="6">
         <f t="shared" si="4"/>
         <v>269981.96383952373</v>
@@ -4865,7 +4965,7 @@
         <v>286180.88166989514</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -4901,7 +5001,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L24" s="234"/>
+      <c r="L24" s="186"/>
       <c r="M24" s="6">
         <f t="shared" si="4"/>
         <v>225338.70675440805</v>
@@ -4911,7 +5011,7 @@
         <v>238859.02915967253</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -4947,7 +5047,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L25" s="235">
+      <c r="L25" s="187">
         <f>77229+250000+38000+(((K25+J25)*0.5))*6</f>
         <v>1184999</v>
       </c>
@@ -4963,7 +5063,7 @@
       <c r="Q25" s="133"/>
       <c r="R25" s="133"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -4999,7 +5099,7 @@
         <f t="shared" si="3"/>
         <v>420000</v>
       </c>
-      <c r="L26" s="234"/>
+      <c r="L26" s="186"/>
       <c r="M26" s="6">
         <f t="shared" si="4"/>
         <v>161621.99266603705</v>
@@ -5009,7 +5109,7 @@
         <v>171319.31222599928</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5045,7 +5145,7 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L27" s="234"/>
+      <c r="L27" s="186"/>
       <c r="M27" s="6">
         <f t="shared" si="4"/>
         <v>474457.03795193206</v>
@@ -5056,7 +5156,7 @@
       </c>
       <c r="R27" s="133"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5092,7 +5192,7 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L28" s="234"/>
+      <c r="L28" s="186"/>
       <c r="M28" s="6">
         <f t="shared" si="4"/>
         <v>469011.1744932076</v>
@@ -5102,7 +5202,7 @@
         <v>497151.84496280004</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5138,7 +5238,7 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L29" s="234"/>
+      <c r="L29" s="186"/>
       <c r="M29" s="6">
         <f t="shared" si="4"/>
         <v>469146.37062336667</v>
@@ -5148,7 +5248,7 @@
         <v>497295.15286076866</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="122" t="s">
         <v>96</v>
       </c>
@@ -5182,7 +5282,7 @@
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L30" s="234"/>
+      <c r="L30" s="186"/>
       <c r="M30" s="6">
         <f t="shared" si="4"/>
         <v>43020.000000000007</v>
@@ -5192,7 +5292,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="122" t="s">
         <v>96</v>
       </c>
@@ -5226,7 +5326,7 @@
         <f t="shared" si="3"/>
         <v>38500.000000000007</v>
       </c>
-      <c r="L31" s="234"/>
+      <c r="L31" s="186"/>
       <c r="M31" s="6">
         <f t="shared" si="4"/>
         <v>43816.666666666672</v>
@@ -5236,7 +5336,7 @@
         <v>46445.666666666672</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="122" t="s">
         <v>96</v>
       </c>
@@ -5280,7 +5380,7 @@
         <v>38001</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="122" t="s">
         <v>96</v>
       </c>
@@ -5324,7 +5424,7 @@
         <v>51512.466666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="122" t="s">
         <v>96</v>
       </c>
@@ -5368,7 +5468,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="122" t="s">
         <v>96</v>
       </c>
@@ -5412,7 +5512,7 @@
         <v>42223.333333333336</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="122" t="s">
         <v>96</v>
       </c>
@@ -5456,7 +5556,7 @@
         <v>42223.333333333336</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="122" t="s">
         <v>96</v>
       </c>
@@ -5500,7 +5600,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="122" t="s">
         <v>96</v>
       </c>
@@ -5544,7 +5644,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="122" t="s">
         <v>96</v>
       </c>
@@ -5588,7 +5688,7 @@
         <v>49823.533333333333</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="122" t="s">
         <v>96</v>
       </c>
@@ -5632,7 +5732,7 @@
         <v>48134.599999999991</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="122" t="s">
         <v>96</v>
       </c>
@@ -5676,7 +5776,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="122" t="s">
         <v>96</v>
       </c>
@@ -5720,7 +5820,7 @@
         <v>46445.666666666672</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="122" t="s">
         <v>96</v>
       </c>
@@ -5765,10 +5865,10 @@
       </c>
       <c r="P43" s="107">
         <f>L1-K52</f>
-        <v>48343.701813001186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1233011.0918130009</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="122" t="s">
         <v>96</v>
       </c>
@@ -5812,7 +5912,7 @@
         <v>51512.466666666667</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="122" t="s">
         <v>96</v>
       </c>
@@ -5856,7 +5956,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="122" t="s">
         <v>96</v>
       </c>
@@ -5903,7 +6003,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="122" t="s">
         <v>96</v>
       </c>
@@ -5952,7 +6052,7 @@
         <v>2011536.666666667</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="122" t="s">
         <v>96</v>
       </c>
@@ -5996,7 +6096,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="122" t="s">
         <v>96</v>
       </c>
@@ -6041,7 +6141,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="122" t="s">
         <v>96</v>
       </c>
@@ -6085,7 +6185,7 @@
         <v>49823.533333333333</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="122" t="s">
         <v>96</v>
       </c>
@@ -6129,7 +6229,7 @@
         <v>48134.599999999991</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="88"/>
       <c r="B52" s="88"/>
       <c r="C52" s="88"/>
@@ -6170,41 +6270,41 @@
       </c>
       <c r="P52" s="130"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K53" s="133">
         <f>K52-L1</f>
-        <v>-48343.701813001186</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="217"/>
-      <c r="D54" s="217"/>
-      <c r="E54" s="217"/>
-      <c r="F54" s="217"/>
-      <c r="G54" s="217"/>
-      <c r="H54" s="217"/>
-      <c r="I54" s="217"/>
-      <c r="J54" s="217"/>
-      <c r="K54" s="217"/>
-      <c r="L54" s="217"/>
-      <c r="M54" s="217"/>
-      <c r="N54" s="217"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="217"/>
-      <c r="D55" s="217"/>
-      <c r="E55" s="217"/>
-      <c r="F55" s="217"/>
-      <c r="G55" s="217"/>
-      <c r="H55" s="217"/>
-      <c r="I55" s="217"/>
-      <c r="J55" s="217"/>
-      <c r="K55" s="217"/>
-      <c r="L55" s="217"/>
-      <c r="M55" s="217"/>
-      <c r="N55" s="217"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-1233011.0918130009</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="226"/>
+      <c r="D54" s="226"/>
+      <c r="E54" s="226"/>
+      <c r="F54" s="226"/>
+      <c r="G54" s="226"/>
+      <c r="H54" s="226"/>
+      <c r="I54" s="226"/>
+      <c r="J54" s="226"/>
+      <c r="K54" s="226"/>
+      <c r="L54" s="226"/>
+      <c r="M54" s="226"/>
+      <c r="N54" s="226"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="226"/>
+      <c r="D55" s="226"/>
+      <c r="E55" s="226"/>
+      <c r="F55" s="226"/>
+      <c r="G55" s="226"/>
+      <c r="H55" s="226"/>
+      <c r="I55" s="226"/>
+      <c r="J55" s="226"/>
+      <c r="K55" s="226"/>
+      <c r="L55" s="226"/>
+      <c r="M55" s="226"/>
+      <c r="N55" s="226"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C56" s="153"/>
       <c r="D56" s="153"/>
       <c r="E56" s="153"/>
@@ -6218,108 +6318,110 @@
       <c r="M56" s="153"/>
       <c r="N56" s="153"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="217" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C57" s="226" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="217"/>
-      <c r="E57" s="217"/>
-      <c r="F57" s="217"/>
-      <c r="G57" s="217"/>
-      <c r="H57" s="217"/>
-      <c r="I57" s="217"/>
-      <c r="J57" s="217"/>
-      <c r="K57" s="217"/>
-      <c r="L57" s="217"/>
-      <c r="M57" s="217"/>
-      <c r="N57" s="217"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="217"/>
-      <c r="D58" s="217"/>
-      <c r="E58" s="217"/>
-      <c r="F58" s="217"/>
-      <c r="G58" s="217"/>
-      <c r="H58" s="217"/>
-      <c r="I58" s="217"/>
-      <c r="J58" s="217"/>
-      <c r="K58" s="217"/>
-      <c r="L58" s="217"/>
-      <c r="M58" s="217"/>
-      <c r="N58" s="217"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="217"/>
-      <c r="D59" s="217"/>
-      <c r="E59" s="217"/>
-      <c r="F59" s="217"/>
-      <c r="G59" s="217"/>
-      <c r="H59" s="217"/>
-      <c r="I59" s="217"/>
-      <c r="J59" s="217"/>
-      <c r="K59" s="217"/>
-      <c r="L59" s="217"/>
-      <c r="M59" s="217"/>
-      <c r="N59" s="217"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="217"/>
-      <c r="D60" s="217"/>
-      <c r="E60" s="217"/>
-      <c r="F60" s="217"/>
-      <c r="G60" s="217"/>
-      <c r="H60" s="217"/>
-      <c r="I60" s="217"/>
-      <c r="J60" s="217"/>
-      <c r="K60" s="217"/>
-      <c r="L60" s="217"/>
-      <c r="M60" s="217"/>
-      <c r="N60" s="217"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="217"/>
-      <c r="D61" s="217"/>
-      <c r="E61" s="217"/>
-      <c r="F61" s="217"/>
-      <c r="G61" s="217"/>
-      <c r="H61" s="217"/>
-      <c r="I61" s="217"/>
-      <c r="J61" s="217"/>
-      <c r="K61" s="217"/>
-      <c r="L61" s="217"/>
-      <c r="M61" s="217"/>
-      <c r="N61" s="217"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="217"/>
-      <c r="D62" s="217"/>
-      <c r="E62" s="217"/>
-      <c r="F62" s="217"/>
-      <c r="G62" s="217"/>
-      <c r="H62" s="217"/>
-      <c r="I62" s="217"/>
-      <c r="J62" s="217"/>
-      <c r="K62" s="217"/>
-      <c r="L62" s="217"/>
-      <c r="M62" s="217"/>
-      <c r="N62" s="217"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="217"/>
-      <c r="D63" s="217"/>
-      <c r="E63" s="217"/>
-      <c r="F63" s="217"/>
-      <c r="G63" s="217"/>
-      <c r="H63" s="217"/>
-      <c r="I63" s="217"/>
-      <c r="J63" s="217"/>
-      <c r="K63" s="217"/>
-      <c r="L63" s="217"/>
-      <c r="M63" s="217"/>
-      <c r="N63" s="217"/>
+      <c r="D57" s="226"/>
+      <c r="E57" s="226"/>
+      <c r="F57" s="226"/>
+      <c r="G57" s="226"/>
+      <c r="H57" s="226"/>
+      <c r="I57" s="226"/>
+      <c r="J57" s="226"/>
+      <c r="K57" s="226"/>
+      <c r="L57" s="226"/>
+      <c r="M57" s="226"/>
+      <c r="N57" s="226"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C58" s="226"/>
+      <c r="D58" s="226"/>
+      <c r="E58" s="226"/>
+      <c r="F58" s="226"/>
+      <c r="G58" s="226"/>
+      <c r="H58" s="226"/>
+      <c r="I58" s="226"/>
+      <c r="J58" s="226"/>
+      <c r="K58" s="226"/>
+      <c r="L58" s="226"/>
+      <c r="M58" s="226"/>
+      <c r="N58" s="226"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C59" s="226"/>
+      <c r="D59" s="226"/>
+      <c r="E59" s="226"/>
+      <c r="F59" s="226"/>
+      <c r="G59" s="226"/>
+      <c r="H59" s="226"/>
+      <c r="I59" s="226"/>
+      <c r="J59" s="226"/>
+      <c r="K59" s="226"/>
+      <c r="L59" s="226"/>
+      <c r="M59" s="226"/>
+      <c r="N59" s="226"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C60" s="226"/>
+      <c r="D60" s="226"/>
+      <c r="E60" s="226"/>
+      <c r="F60" s="226"/>
+      <c r="G60" s="226"/>
+      <c r="H60" s="226"/>
+      <c r="I60" s="226"/>
+      <c r="J60" s="226"/>
+      <c r="K60" s="226"/>
+      <c r="L60" s="226"/>
+      <c r="M60" s="226"/>
+      <c r="N60" s="226"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C61" s="226"/>
+      <c r="D61" s="226"/>
+      <c r="E61" s="226"/>
+      <c r="F61" s="226"/>
+      <c r="G61" s="226"/>
+      <c r="H61" s="226"/>
+      <c r="I61" s="226"/>
+      <c r="J61" s="226"/>
+      <c r="K61" s="226"/>
+      <c r="L61" s="226"/>
+      <c r="M61" s="226"/>
+      <c r="N61" s="226"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C62" s="226"/>
+      <c r="D62" s="226"/>
+      <c r="E62" s="226"/>
+      <c r="F62" s="226"/>
+      <c r="G62" s="226"/>
+      <c r="H62" s="226"/>
+      <c r="I62" s="226"/>
+      <c r="J62" s="226"/>
+      <c r="K62" s="226"/>
+      <c r="L62" s="226"/>
+      <c r="M62" s="226"/>
+      <c r="N62" s="226"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C63" s="226"/>
+      <c r="D63" s="226"/>
+      <c r="E63" s="226"/>
+      <c r="F63" s="226"/>
+      <c r="G63" s="226"/>
+      <c r="H63" s="226"/>
+      <c r="I63" s="226"/>
+      <c r="J63" s="226"/>
+      <c r="K63" s="226"/>
+      <c r="L63" s="226"/>
+      <c r="M63" s="226"/>
+      <c r="N63" s="226"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6336,8 +6438,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6347,17 +6447,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>144</v>
       </c>
@@ -6365,7 +6465,7 @@
         <v>-447223.45918396302</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>145</v>
       </c>
@@ -6373,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>146</v>
       </c>
@@ -6381,7 +6481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>147</v>
       </c>
@@ -6389,12 +6489,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>144</v>
       </c>
@@ -6402,7 +6502,7 @@
         <v>451182</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>145</v>
       </c>
@@ -6410,7 +6510,7 @@
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>146</v>
       </c>
@@ -6418,7 +6518,7 @@
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>147</v>
       </c>
@@ -6426,7 +6526,7 @@
         <v>37598.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C16" s="3" t="s">
         <v>148</v>
       </c>
@@ -6436,7 +6536,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>144</v>
       </c>
@@ -6445,7 +6545,7 @@
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>145</v>
       </c>
@@ -6453,7 +6553,7 @@
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>146</v>
       </c>
@@ -6461,7 +6561,7 @@
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>147</v>
       </c>
@@ -6469,7 +6569,7 @@
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
         <v>151</v>
       </c>
@@ -6477,26 +6577,26 @@
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="226" t="s">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C22" s="250" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="229">
+      <c r="D22" s="253">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="227"/>
-      <c r="D23" s="230"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="227"/>
-      <c r="D24" s="230"/>
-    </row>
-    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="228"/>
-      <c r="D25" s="231"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C23" s="251"/>
+      <c r="D23" s="254"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C24" s="251"/>
+      <c r="D24" s="254"/>
+    </row>
+    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="252"/>
+      <c r="D25" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6511,16 +6611,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -6540,11 +6640,11 @@
       <c r="M1" s="48"/>
       <c r="N1" s="51" t="str">
         <f>RESUMEN!C5</f>
-        <v>VTO: 14/11</v>
+        <v>VTO: 15/12</v>
       </c>
       <c r="O1" s="51"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="48"/>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
@@ -6563,7 +6663,7 @@
       <c r="N2" s="48"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="48"/>
       <c r="B3" s="50"/>
       <c r="C3" s="50"/>
@@ -6586,7 +6686,7 @@
       </c>
       <c r="O3" s="53"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="48"/>
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
@@ -6607,11 +6707,11 @@
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
     </row>
-    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="232" t="s">
+    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="256" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="232" t="s">
+      <c r="B5" s="256" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="54" t="s">
@@ -6623,7 +6723,7 @@
       <c r="E5" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="232" t="s">
+      <c r="F5" s="256" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="36" t="s">
@@ -6645,16 +6745,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="40"/>
-      <c r="N5" s="232" t="s">
+      <c r="N5" s="256" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="232" t="s">
+      <c r="O5" s="256" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="233"/>
-      <c r="B6" s="233"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="257"/>
+      <c r="B6" s="257"/>
       <c r="C6" s="55" t="s">
         <v>80</v>
       </c>
@@ -6664,7 +6764,7 @@
       <c r="E6" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="233"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="43" t="s">
         <v>81</v>
       </c>
@@ -6684,10 +6784,10 @@
         <v>84</v>
       </c>
       <c r="M6" s="46"/>
-      <c r="N6" s="233"/>
-      <c r="O6" s="233"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="257"/>
+      <c r="O6" s="257"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>1</v>
       </c>
@@ -6733,7 +6833,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>2</v>
       </c>
@@ -6779,7 +6879,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>3</v>
       </c>
@@ -6825,7 +6925,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>4</v>
       </c>
@@ -6871,7 +6971,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>5</v>
       </c>
@@ -6917,7 +7017,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>6</v>
       </c>
@@ -6963,7 +7063,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>7</v>
       </c>
@@ -7009,7 +7109,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>8</v>
       </c>
@@ -7055,7 +7155,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>9</v>
       </c>
@@ -7101,7 +7201,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>10</v>
       </c>
@@ -7147,7 +7247,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
         <v>11</v>
       </c>
@@ -7193,7 +7293,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>12</v>
       </c>
@@ -7239,7 +7339,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>13</v>
       </c>
@@ -7285,7 +7385,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>14</v>
       </c>
@@ -7331,7 +7431,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
         <v>15</v>
       </c>
@@ -7377,7 +7477,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>16</v>
       </c>
@@ -7423,7 +7523,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>17</v>
       </c>
@@ -7469,7 +7569,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>18</v>
       </c>
@@ -7515,7 +7615,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
         <v>19</v>
       </c>
@@ -7561,7 +7661,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>20</v>
       </c>
@@ -7607,7 +7707,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>21</v>
       </c>
@@ -7653,7 +7753,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>22</v>
       </c>
@@ -7699,7 +7799,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
@@ -7716,7 +7816,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="56">
@@ -7757,7 +7857,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E33" s="32"/>
       <c r="F33" s="32"/>
     </row>

--- a/BELGRANO 1646/Noviembre/Noviembre-BLG1646.xlsx
+++ b/BELGRANO 1646/Noviembre/Noviembre-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EC2A0F-B361-41A9-9BA0-EC62B236F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A31C32-FDB7-4C0A-8686-79C83551A41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$119</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="172">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -523,46 +523,7 @@
     <t>GASTOS PARTICULARES</t>
   </si>
   <si>
-    <t>Contessi - Provision y colocacion de tres tubos de luz led en cabinas de los acensores</t>
-  </si>
-  <si>
-    <t>Ferreteria el herrero - Lamparas, pico, pinceleta, rodillo, aguarras x3, cinta, silicona, etc</t>
-  </si>
-  <si>
-    <t>Numero 1859135 Debito automatico 01/10</t>
-  </si>
-  <si>
-    <t>Debito 02/10</t>
-  </si>
-  <si>
-    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 06/10</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 08/10</t>
-  </si>
-  <si>
-    <t>Debito 13/10</t>
-  </si>
-  <si>
-    <t>Debito 24/10</t>
-  </si>
-  <si>
-    <t>Fumigacion 28/10</t>
-  </si>
-  <si>
     <t>Energroup - SERVICE DE MANTENIMIENTO PREVENTIVO</t>
-  </si>
-  <si>
-    <t>Energroup - SERVICIO CORRECTIVO CAMBIO DE BATERIAS POR 2 UNIDADES DE 180 AMP</t>
-  </si>
-  <si>
-    <t>Medianera Mural - Reparacion de sellados de vidrios (frente y contrafrente) departamentos "A" en pisos 12, 10, 8 y 3 - 09/10</t>
-  </si>
-  <si>
-    <t>Cartas de documento 11A</t>
-  </si>
-  <si>
-    <t>Envios cartas documento</t>
   </si>
   <si>
     <t>Las expensas extraordinarias ascendieron a un total de $2.900.000. Sin embargo, considerando que pasar de un prorrateo de $450.000 a dicho monto implicaría un incremento significativo en el valor final de las expensas, se resolvió distribuir este importe en tres cuotas.
@@ -581,16 +542,43 @@
     <t>Ingreso mes de OCTUBRE</t>
   </si>
   <si>
-    <t>Servisur - 10 plafones 12w en escaleras y 5</t>
-  </si>
-  <si>
-    <t>Distribuidora Barbieiro</t>
-  </si>
-  <si>
     <t>Pintureria Ogus - Sinteplast, Albaalatex, pincel, Enduido, etc</t>
   </si>
   <si>
     <t>Gamboa gustavo - Trabajo realizado - Limpieza de zona afectada en zingueria, sellado de grietas con filtraciones con membrana transparente</t>
+  </si>
+  <si>
+    <t>Numero 1859135 Debito automatico 03/11</t>
+  </si>
+  <si>
+    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 06/11</t>
+  </si>
+  <si>
+    <t>Debito 04/11</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 07/11</t>
+  </si>
+  <si>
+    <t>Servisur - 10 plafones 12w en escaleras y 5 luces en altura</t>
+  </si>
+  <si>
+    <t>Debito 12/11</t>
+  </si>
+  <si>
+    <t>Debito 26/11</t>
+  </si>
+  <si>
+    <t>Fumigacion 26/11</t>
+  </si>
+  <si>
+    <t>Limpieza de pileta - Cambio de bomba - Armado de tablero - Cambio de colector, de filtro - Mano de obra y materiales</t>
+  </si>
+  <si>
+    <t>Riesgo Uno - Recambio de valvula de retencion sistema de bomba - Desarme de equipo, reemplazo de elemnto aberiado, calibracion y puesta en marcha</t>
+  </si>
+  <si>
+    <t>Distribuidora Barbieiro - Compra de materiales electricos</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1306,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="263">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1546,10 +1534,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1571,11 +1556,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="15" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1598,6 +1578,16 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="19" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1673,27 +1663,36 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1775,11 +1774,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2145,24 +2139,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P134"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P129"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="96" t="s">
         <v>118</v>
@@ -2171,7 +2165,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
         <v>0</v>
@@ -2180,7 +2174,7 @@
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="s">
         <v>88</v>
@@ -2189,7 +2183,7 @@
       <c r="D3" s="67"/>
       <c r="E3" s="68"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="66"/>
       <c r="B4" s="67" t="s">
         <v>89</v>
@@ -2198,20 +2192,20 @@
       <c r="D4" s="67"/>
       <c r="E4" s="68"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="70" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D5" s="70"/>
       <c r="E5" s="71"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66" t="s">
         <v>99</v>
       </c>
@@ -2220,7 +2214,7 @@
       <c r="D6" s="67"/>
       <c r="E6" s="68"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="69" t="s">
         <v>98</v>
       </c>
@@ -2229,158 +2223,158 @@
       <c r="D7" s="70"/>
       <c r="E7" s="71"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="201" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="205" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="202"/>
-      <c r="D14" s="203"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="204"/>
-      <c r="C15" s="205"/>
-      <c r="D15" s="206"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="204"/>
-      <c r="C16" s="205"/>
-      <c r="D16" s="206"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="207"/>
-      <c r="C17" s="208"/>
-      <c r="D17" s="209"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="206"/>
+      <c r="D14" s="207"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="208"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="210"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="208"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="210"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="211"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="213"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="60" t="s">
         <v>86</v>
       </c>
       <c r="B21" s="61"/>
       <c r="C21" s="62"/>
       <c r="D21" s="58"/>
-      <c r="E21" s="177" t="s">
+      <c r="E21" s="174" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="178" t="s">
+      <c r="F21" s="175" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="119" t="s">
         <v>142</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="125"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E22" s="173"/>
+      <c r="F22" s="173"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="119" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="163">
-        <v>1376395.8</v>
+      <c r="D23" s="196">
+        <v>1395571.4</v>
       </c>
       <c r="E23" s="129">
         <f>D23*91.91%</f>
-        <v>1265045.3797799998</v>
+        <v>1282669.6737399998</v>
       </c>
       <c r="F23" s="129">
         <f>D23*8.09%</f>
-        <v>111350.42022</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>112901.72626</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="119" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="163">
-        <v>-299366.09000000003</v>
+      <c r="D24" s="196">
+        <v>-303536.77</v>
       </c>
       <c r="E24" s="129">
         <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
-        <v>-275147.37331900001</v>
+        <v>-278980.64530699997</v>
       </c>
       <c r="F24" s="129">
         <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
-        <v>-24218.716681000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-24556.124693000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="119" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="163">
-        <v>0.28999999999999998</v>
+      <c r="D25" s="196">
+        <v>0.37</v>
       </c>
       <c r="E25" s="129">
         <f t="shared" si="0"/>
-        <v>0.26653899999999997</v>
+        <v>0.34006699999999995</v>
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>2.3460999999999999E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2.9932999999999998E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="119"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="163"/>
+      <c r="D26" s="196"/>
       <c r="E26" s="129"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="94" t="s">
         <v>3</v>
       </c>
       <c r="B27" s="94"/>
       <c r="C27" s="94"/>
-      <c r="D27" s="106">
+      <c r="D27" s="197">
         <f>SUM(D23:D26)</f>
-        <v>1077030</v>
+        <v>1092035</v>
       </c>
       <c r="E27" s="106">
         <f>SUM(E23:E26)</f>
-        <v>989898.27299999981</v>
+        <v>1003689.3684999997</v>
       </c>
       <c r="F27" s="106">
         <f>SUM(F23:F26)</f>
-        <v>87131.726999999999</v>
+        <v>88345.631499999989</v>
       </c>
       <c r="G27" s="107">
         <f>E27+F27</f>
-        <v>1077029.9999999998</v>
+        <v>1092034.9999999998</v>
       </c>
       <c r="H27" s="142" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="93" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="164">
+      <c r="D28" s="198">
         <v>0</v>
       </c>
       <c r="E28" s="129">
@@ -2393,11 +2387,11 @@
       </c>
       <c r="H28" s="142"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="93"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="163">
+      <c r="D29" s="196">
         <v>0</v>
       </c>
       <c r="E29" s="129">
@@ -2410,31 +2404,31 @@
       </c>
       <c r="H29" s="142"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="93"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="163"/>
+      <c r="D30" s="196"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="H30" s="142"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="93"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="163"/>
+      <c r="D31" s="196"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="H31" s="142"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="94" t="s">
         <v>117</v>
       </c>
       <c r="B32" s="94"/>
       <c r="C32" s="94"/>
-      <c r="D32" s="106">
+      <c r="D32" s="197">
         <f>SUM(D28:D30)</f>
         <v>0</v>
       </c>
@@ -2455,13 +2449,13 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="93" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="164"/>
+      <c r="D33" s="198"/>
       <c r="E33" s="129">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2472,13 +2466,13 @@
       </c>
       <c r="H33" s="142"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="163"/>
+      <c r="D34" s="196"/>
       <c r="E34" s="129">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2489,13 +2483,13 @@
       </c>
       <c r="H34" s="142"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="93" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="163"/>
+      <c r="D35" s="196"/>
       <c r="E35" s="129">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2506,13 +2500,13 @@
       </c>
       <c r="H35" s="142"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="94" t="s">
         <v>110</v>
       </c>
       <c r="B36" s="94"/>
       <c r="C36" s="94"/>
-      <c r="D36" s="106">
+      <c r="D36" s="197">
         <f>SUM(D29:D35)</f>
         <v>0</v>
       </c>
@@ -2526,40 +2520,40 @@
       </c>
       <c r="H36" s="142"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="124"/>
       <c r="B37" s="97"/>
       <c r="C37" s="97"/>
-      <c r="D37" s="163"/>
+      <c r="D37" s="196"/>
       <c r="E37" s="118"/>
       <c r="F37" s="118"/>
       <c r="H37" s="142"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="124"/>
       <c r="B38" s="97"/>
       <c r="C38" s="97"/>
-      <c r="D38" s="163"/>
+      <c r="D38" s="196"/>
       <c r="E38" s="118"/>
       <c r="F38" s="118"/>
       <c r="H38" s="142"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="97"/>
       <c r="B39" s="97"/>
       <c r="C39" s="109"/>
-      <c r="D39" s="163"/>
+      <c r="D39" s="196"/>
       <c r="E39" s="118"/>
       <c r="F39" s="118"/>
       <c r="H39" s="142"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="94" t="s">
         <v>117</v>
       </c>
       <c r="B40" s="94"/>
       <c r="C40" s="94"/>
-      <c r="D40" s="106"/>
+      <c r="D40" s="197"/>
       <c r="E40" s="110">
         <f>SUM(D37:D39)</f>
         <v>0</v>
@@ -2570,11 +2564,11 @@
       </c>
       <c r="H40" s="142"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="93"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="111"/>
+      <c r="D41" s="199"/>
       <c r="E41" s="129">
         <f>D41*91.91%</f>
         <v>0</v>
@@ -2585,11 +2579,11 @@
       </c>
       <c r="H41" s="142"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="93"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="111"/>
+      <c r="D42" s="199"/>
       <c r="E42" s="129">
         <f>D42*91.91%</f>
         <v>0</v>
@@ -2600,11 +2594,11 @@
       </c>
       <c r="H42" s="142"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="93"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="166"/>
+      <c r="D43" s="200"/>
       <c r="E43" s="129">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2615,13 +2609,13 @@
       </c>
       <c r="H43" s="142"/>
     </row>
-    <row r="44" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="94" t="s">
         <v>127</v>
       </c>
       <c r="B44" s="94"/>
       <c r="C44" s="94"/>
-      <c r="D44" s="106">
+      <c r="D44" s="197">
         <f>SUM(D41:D43)</f>
         <v>0</v>
       </c>
@@ -2639,24 +2633,24 @@
       </c>
       <c r="H44" s="142"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="93" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="166"/>
+      <c r="D45" s="200"/>
       <c r="E45" s="112"/>
       <c r="F45" s="99"/>
       <c r="H45" s="142"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="93" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="97"/>
-      <c r="D46" s="111">
+      <c r="D46" s="199">
         <v>5020</v>
       </c>
       <c r="E46" s="129">
@@ -2669,15 +2663,15 @@
       </c>
       <c r="H46" s="142"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="93" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="173">
+      <c r="D47" s="199">
         <f>115317.73+6881.98+61937.82</f>
         <v>184137.53</v>
       </c>
@@ -2691,15 +2685,15 @@
       </c>
       <c r="H47" s="142"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="93" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="97" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="173">
+      <c r="D48" s="199">
         <v>609845.93000000005</v>
       </c>
       <c r="E48" s="129">
@@ -2712,13 +2706,13 @@
       </c>
       <c r="H48" s="142"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="94" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="95"/>
       <c r="C49" s="95"/>
-      <c r="D49" s="106">
+      <c r="D49" s="197">
         <f>SUM(D46:D48)</f>
         <v>799003.46000000008</v>
       </c>
@@ -2739,218 +2733,264 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="166"/>
+      <c r="D50" s="200"/>
       <c r="E50" s="113"/>
       <c r="F50" s="7"/>
       <c r="H50" s="142"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="170" t="s">
-        <v>153</v>
+    <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="167" t="s">
+        <v>138</v>
       </c>
       <c r="B51" s="159"/>
       <c r="C51" s="160"/>
-      <c r="D51" s="166">
-        <v>39000</v>
+      <c r="D51" s="199">
+        <v>372000</v>
       </c>
       <c r="E51" s="141">
         <f>D51</f>
-        <v>39000</v>
+        <v>372000</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="107">
         <f>D51</f>
-        <v>39000</v>
+        <v>372000</v>
       </c>
       <c r="H51" s="148">
         <f>E51+F51</f>
-        <v>39000</v>
-      </c>
-      <c r="I51" s="161"/>
+        <v>372000</v>
+      </c>
+      <c r="I51" s="161">
+        <f>H51-D51</f>
+        <v>0</v>
+      </c>
       <c r="J51" s="161"/>
     </row>
-    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="170" t="s">
-        <v>138</v>
-      </c>
-      <c r="B52" s="159"/>
-      <c r="C52" s="160"/>
-      <c r="D52" s="173">
-        <v>372000</v>
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="149"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="199">
+        <v>185303.46</v>
       </c>
       <c r="E52" s="141">
-        <f>D52</f>
-        <v>372000</v>
-      </c>
-      <c r="F52" s="7"/>
+        <f t="shared" ref="E52:E57" si="7">D52*91.91%</f>
+        <v>170312.41008599999</v>
+      </c>
+      <c r="F52" s="129">
+        <f t="shared" ref="F52:F57" si="8">D52*8.09%</f>
+        <v>14991.049913999999</v>
+      </c>
       <c r="G52" s="107">
-        <f>D52</f>
-        <v>372000</v>
+        <f t="shared" ref="G52:G64" si="9">D52</f>
+        <v>185303.46</v>
       </c>
       <c r="H52" s="148">
-        <f>E52+F52</f>
-        <v>372000</v>
-      </c>
-      <c r="I52" s="161">
-        <f>H52-D52</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="H52:H64" si="10">E52+F52</f>
+        <v>185303.46</v>
+      </c>
+      <c r="I52" s="161"/>
       <c r="J52" s="161"/>
     </row>
-    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="119" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53" s="149"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="173">
-        <v>153143.35</v>
+    <row r="53" spans="1:16" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="225" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" s="226"/>
+      <c r="C53" s="227"/>
+      <c r="D53" s="199">
+        <v>261299.98</v>
       </c>
       <c r="E53" s="141">
-        <f t="shared" ref="E53:E60" si="7">D53*91.91%</f>
-        <v>140754.05298499999</v>
+        <f t="shared" si="7"/>
+        <v>240160.81161799998</v>
       </c>
       <c r="F53" s="129">
-        <f t="shared" ref="F53:F60" si="8">D53*8.09%</f>
-        <v>12389.297015</v>
+        <f t="shared" si="8"/>
+        <v>21139.168382</v>
       </c>
       <c r="G53" s="107">
-        <f t="shared" ref="G53:G67" si="9">D53</f>
-        <v>153143.35</v>
+        <f t="shared" si="9"/>
+        <v>261299.98</v>
       </c>
       <c r="H53" s="148">
-        <f t="shared" ref="H53:H67" si="10">E53+F53</f>
-        <v>153143.34999999998</v>
+        <f t="shared" si="10"/>
+        <v>261299.97999999998</v>
       </c>
       <c r="I53" s="161"/>
       <c r="J53" s="161"/>
     </row>
-    <row r="54" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="262" t="s">
-        <v>8</v>
-      </c>
-      <c r="B54" s="149"/>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="93" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="173">
-        <v>1132015.98</v>
-      </c>
-      <c r="E54" s="141"/>
-      <c r="F54" s="129"/>
-      <c r="G54" s="107"/>
-      <c r="H54" s="148"/>
-      <c r="I54" s="161"/>
-      <c r="J54" s="161"/>
-    </row>
-    <row r="55" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="262" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55" s="149"/>
+      <c r="D54" s="199">
+        <v>148200</v>
+      </c>
+      <c r="E54" s="141">
+        <f t="shared" si="7"/>
+        <v>136210.62</v>
+      </c>
+      <c r="F54" s="129">
+        <f t="shared" si="8"/>
+        <v>11989.38</v>
+      </c>
+      <c r="G54" s="107">
+        <f t="shared" si="9"/>
+        <v>148200</v>
+      </c>
+      <c r="H54" s="148">
+        <f t="shared" si="10"/>
+        <v>148200</v>
+      </c>
+      <c r="I54" s="161">
+        <f t="shared" ref="I54:I63" si="11">H54-D54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="161">
+        <f t="shared" ref="J54:J63" si="12">G54-D54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>161</v>
+      </c>
       <c r="C55" s="7"/>
-      <c r="D55" s="173">
-        <v>261299.98</v>
-      </c>
-      <c r="E55" s="141"/>
-      <c r="F55" s="129"/>
-      <c r="G55" s="107"/>
-      <c r="H55" s="148"/>
-      <c r="I55" s="161"/>
-      <c r="J55" s="161"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D55" s="199">
+        <v>129320</v>
+      </c>
+      <c r="E55" s="141">
+        <f>D55*91.91%</f>
+        <v>118858.01199999999</v>
+      </c>
+      <c r="F55" s="129">
+        <f t="shared" si="8"/>
+        <v>10461.987999999999</v>
+      </c>
+      <c r="G55" s="107">
+        <f t="shared" si="9"/>
+        <v>129320</v>
+      </c>
+      <c r="H55" s="148">
+        <f>E55+F55</f>
+        <v>129319.99999999999</v>
+      </c>
+      <c r="I55" s="161">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="93" t="s">
-        <v>162</v>
-      </c>
-      <c r="B56" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="B56" s="97" t="s">
+        <v>163</v>
+      </c>
       <c r="C56" s="7"/>
-      <c r="D56" s="173">
-        <v>120000</v>
+      <c r="D56" s="199">
+        <v>655067.85</v>
       </c>
       <c r="E56" s="141">
         <f t="shared" si="7"/>
-        <v>110291.99999999999</v>
+        <v>602072.86093499989</v>
       </c>
       <c r="F56" s="129">
         <f t="shared" si="8"/>
-        <v>9708</v>
+        <v>52994.989064999994</v>
       </c>
       <c r="G56" s="107">
         <f t="shared" si="9"/>
-        <v>120000</v>
+        <v>655067.85</v>
       </c>
       <c r="H56" s="148">
         <f t="shared" si="10"/>
-        <v>119999.99999999999</v>
+        <v>655067.84999999986</v>
       </c>
       <c r="I56" s="161">
-        <f t="shared" ref="I56:I66" si="11">H56-D56</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J56" s="161">
-        <f t="shared" ref="J56:J66" si="12">G56-D56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="261" t="s">
-        <v>163</v>
-      </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="173">
-        <v>175450</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="124" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" s="97" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" s="97"/>
+      <c r="D57" s="199">
+        <v>1068743.0900000001</v>
       </c>
       <c r="E57" s="141">
         <f t="shared" si="7"/>
-        <v>161256.09499999997</v>
+        <v>982281.774019</v>
       </c>
       <c r="F57" s="129">
         <f t="shared" si="8"/>
-        <v>14193.905000000001</v>
+        <v>86461.315981000007</v>
       </c>
       <c r="G57" s="107">
         <f t="shared" si="9"/>
-        <v>175450</v>
+        <v>1068743.0900000001</v>
       </c>
       <c r="H57" s="148">
         <f t="shared" si="10"/>
-        <v>175449.99999999997</v>
-      </c>
-      <c r="I57" s="161"/>
-      <c r="J57" s="161"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="93" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="111">
-        <v>129320</v>
+        <v>1068743.0900000001</v>
+      </c>
+      <c r="I57" s="161">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="222" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="223"/>
+      <c r="C58" s="224"/>
+      <c r="D58" s="199">
+        <v>52100</v>
       </c>
       <c r="E58" s="141">
-        <f>D58*91.91%</f>
-        <v>118858.01199999999</v>
-      </c>
-      <c r="F58" s="129">
-        <f t="shared" si="8"/>
-        <v>10461.987999999999</v>
-      </c>
+        <f t="shared" ref="E58" si="13">D58</f>
+        <v>52100</v>
+      </c>
+      <c r="F58" s="129"/>
       <c r="G58" s="107">
         <f t="shared" si="9"/>
-        <v>129320</v>
+        <v>52100</v>
       </c>
       <c r="H58" s="148">
-        <f>E58+F58</f>
-        <v>129319.99999999999</v>
+        <f t="shared" si="10"/>
+        <v>52100</v>
       </c>
       <c r="I58" s="161">
         <f t="shared" si="11"/>
@@ -2961,32 +3001,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" s="97" t="s">
-        <v>156</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="173">
-        <v>655067.85</v>
+    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="228" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="229"/>
+      <c r="C59" s="230"/>
+      <c r="D59" s="199">
+        <v>400000</v>
       </c>
       <c r="E59" s="141">
-        <f t="shared" si="7"/>
-        <v>602072.86093499989</v>
+        <f t="shared" ref="E59:E60" si="14">D59*91.91%</f>
+        <v>367639.99999999994</v>
       </c>
       <c r="F59" s="129">
-        <f t="shared" si="8"/>
-        <v>52994.989064999994</v>
+        <f t="shared" ref="F59:F60" si="15">D59*8.09%</f>
+        <v>32360</v>
       </c>
       <c r="G59" s="107">
         <f t="shared" si="9"/>
-        <v>655067.85</v>
+        <v>400000</v>
       </c>
       <c r="H59" s="148">
         <f t="shared" si="10"/>
-        <v>655067.84999999986</v>
+        <v>399999.99999999994</v>
       </c>
       <c r="I59" s="161">
         <f t="shared" si="11"/>
@@ -2996,33 +3034,39 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="124" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" s="97" t="s">
-        <v>160</v>
-      </c>
+      <c r="M59" s="169" t="s">
+        <v>137</v>
+      </c>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="170">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="176" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="97"/>
       <c r="C60" s="97"/>
-      <c r="D60" s="111">
-        <v>1107047.99</v>
+      <c r="D60" s="199">
+        <v>77541.55</v>
       </c>
       <c r="E60" s="141">
-        <f t="shared" si="7"/>
-        <v>1017487.8076089999</v>
+        <f t="shared" si="14"/>
+        <v>71268.438605000003</v>
       </c>
       <c r="F60" s="129">
-        <f t="shared" si="8"/>
-        <v>89560.182390999995</v>
+        <f t="shared" si="15"/>
+        <v>6273.1113949999999</v>
       </c>
       <c r="G60" s="107">
         <f t="shared" si="9"/>
-        <v>1107047.99</v>
+        <v>77541.55</v>
       </c>
       <c r="H60" s="148">
         <f t="shared" si="10"/>
-        <v>1107047.99</v>
+        <v>77541.55</v>
       </c>
       <c r="I60" s="161">
         <f t="shared" si="11"/>
@@ -3032,104 +3076,77 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="218" t="s">
-        <v>161</v>
-      </c>
-      <c r="B61" s="219"/>
-      <c r="C61" s="220"/>
-      <c r="D61" s="111">
-        <v>51000</v>
+      <c r="M60" s="193"/>
+      <c r="P60" s="194"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="195" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="97"/>
+      <c r="C61" s="97"/>
+      <c r="D61" s="199">
+        <v>185000</v>
       </c>
       <c r="E61" s="141">
-        <f t="shared" ref="E61" si="13">D61</f>
-        <v>51000</v>
+        <f t="shared" ref="E61:E64" si="16">D61</f>
+        <v>185000</v>
       </c>
       <c r="F61" s="129"/>
       <c r="G61" s="107">
         <f t="shared" si="9"/>
-        <v>51000</v>
+        <v>185000</v>
       </c>
       <c r="H61" s="148">
         <f t="shared" si="10"/>
-        <v>51000</v>
-      </c>
-      <c r="I61" s="161">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="179" t="s">
-        <v>175</v>
+        <v>185000</v>
+      </c>
+      <c r="I61" s="161"/>
+      <c r="J61" s="161"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="97" t="s">
+        <v>171</v>
       </c>
       <c r="B62" s="97"/>
       <c r="C62" s="97"/>
-      <c r="D62" s="173">
-        <v>400000</v>
+      <c r="D62" s="199">
+        <v>88795.1</v>
       </c>
       <c r="E62" s="141">
-        <f t="shared" ref="E62:E67" si="14">D62*91.91%</f>
-        <v>367639.99999999994</v>
-      </c>
-      <c r="F62" s="129">
-        <f t="shared" ref="F62:F67" si="15">D62*8.09%</f>
-        <v>32360</v>
-      </c>
+        <f t="shared" si="16"/>
+        <v>88795.1</v>
+      </c>
+      <c r="F62" s="129"/>
       <c r="G62" s="107">
         <f t="shared" si="9"/>
-        <v>400000</v>
-      </c>
-      <c r="H62" s="148">
-        <f t="shared" si="10"/>
-        <v>399999.99999999994</v>
-      </c>
-      <c r="I62" s="161">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M62" s="172" t="s">
-        <v>137</v>
-      </c>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="173">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="179" t="s">
-        <v>174</v>
-      </c>
-      <c r="B63" s="97"/>
-      <c r="C63" s="97"/>
-      <c r="D63" s="173">
-        <v>77541.55</v>
+        <v>88795.1</v>
+      </c>
+      <c r="H62" s="148"/>
+      <c r="I62" s="161"/>
+      <c r="J62" s="161"/>
+    </row>
+    <row r="63" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="199">
+        <v>88294</v>
       </c>
       <c r="E63" s="141">
-        <f t="shared" si="14"/>
-        <v>71268.438605000003</v>
-      </c>
-      <c r="F63" s="129">
-        <f t="shared" si="15"/>
-        <v>6273.1113949999999</v>
-      </c>
+        <f t="shared" si="16"/>
+        <v>88294</v>
+      </c>
+      <c r="F63" s="129"/>
       <c r="G63" s="107">
         <f t="shared" si="9"/>
-        <v>77541.55</v>
+        <v>88294</v>
       </c>
       <c r="H63" s="148">
         <f t="shared" si="10"/>
-        <v>77541.55</v>
+        <v>88294</v>
       </c>
       <c r="I63" s="161">
         <f t="shared" si="11"/>
@@ -3139,860 +3156,747 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M63" s="258"/>
-      <c r="N63" s="259"/>
-      <c r="O63" s="259"/>
-      <c r="P63" s="260"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" s="172" t="s">
-        <v>172</v>
-      </c>
-      <c r="B64" s="97"/>
-      <c r="C64" s="97"/>
-      <c r="D64" s="173">
-        <v>185000</v>
+    </row>
+    <row r="64" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="222" t="s">
+        <v>169</v>
+      </c>
+      <c r="B64" s="223"/>
+      <c r="C64" s="224"/>
+      <c r="D64" s="199">
+        <v>1500000</v>
       </c>
       <c r="E64" s="141">
-        <f t="shared" ref="E64:E66" si="16">D64</f>
-        <v>185000</v>
+        <f t="shared" si="16"/>
+        <v>1500000</v>
       </c>
       <c r="F64" s="129"/>
       <c r="G64" s="107">
         <f t="shared" si="9"/>
-        <v>185000</v>
+        <v>1500000</v>
       </c>
       <c r="H64" s="148">
         <f t="shared" si="10"/>
-        <v>185000</v>
+        <v>1500000</v>
       </c>
       <c r="I64" s="161"/>
       <c r="J64" s="161"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="172" t="s">
-        <v>173</v>
-      </c>
-      <c r="B65" s="97"/>
-      <c r="C65" s="97"/>
-      <c r="D65" s="173">
-        <v>85795.1</v>
-      </c>
-      <c r="E65" s="141"/>
-      <c r="F65" s="129"/>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="95"/>
+      <c r="C65" s="95"/>
+      <c r="D65" s="197">
+        <f>SUM(D51:D64)</f>
+        <v>5211665.0299999993</v>
+      </c>
+      <c r="E65" s="106">
+        <f>SUM(E51:E64)</f>
+        <v>4974994.0272629997</v>
+      </c>
+      <c r="F65" s="106">
+        <f>SUM(F51:F64)</f>
+        <v>236671.002737</v>
+      </c>
       <c r="G65" s="107">
-        <f t="shared" si="9"/>
-        <v>85795.1</v>
-      </c>
-      <c r="H65" s="148"/>
-      <c r="I65" s="161"/>
-      <c r="J65" s="161"/>
-    </row>
-    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
-        <v>119</v>
-      </c>
+        <f>E65+F65</f>
+        <v>5211665.0299999993</v>
+      </c>
+      <c r="H65" s="142" t="str">
+        <f>IF(D65=G65, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I65" s="161">
+        <f>D65-G65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="111">
-        <v>88294</v>
-      </c>
-      <c r="E66" s="141">
-        <f t="shared" si="16"/>
-        <v>88294</v>
-      </c>
-      <c r="F66" s="129"/>
-      <c r="G66" s="107">
-        <f t="shared" si="9"/>
-        <v>88294</v>
-      </c>
-      <c r="H66" s="148">
-        <f t="shared" si="10"/>
-        <v>88294</v>
-      </c>
-      <c r="I66" s="161">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="119" t="s">
-        <v>154</v>
-      </c>
-      <c r="B67" s="112"/>
+      <c r="D66" s="200"/>
+      <c r="E66" s="113"/>
+      <c r="F66" s="7"/>
+      <c r="H66" s="142"/>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
       <c r="C67" s="7"/>
-      <c r="D67" s="111">
-        <v>90143.44</v>
-      </c>
-      <c r="E67" s="141">
-        <f t="shared" si="14"/>
-        <v>82850.835703999997</v>
-      </c>
-      <c r="F67" s="129">
-        <f t="shared" si="15"/>
-        <v>7292.6042960000004</v>
-      </c>
-      <c r="G67" s="107">
-        <f t="shared" si="9"/>
-        <v>90143.44</v>
-      </c>
-      <c r="H67" s="148">
-        <f t="shared" si="10"/>
-        <v>90143.44</v>
-      </c>
-      <c r="I67" s="161"/>
-      <c r="J67" s="161"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="94" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68" s="95"/>
-      <c r="C68" s="95"/>
-      <c r="D68" s="106">
-        <f>SUM(D51:D67)</f>
-        <v>5122119.24</v>
-      </c>
-      <c r="E68" s="106">
-        <f>SUM(E51:E67)</f>
-        <v>3407774.1028379998</v>
-      </c>
-      <c r="F68" s="106">
-        <f>SUM(F51:F67)</f>
-        <v>235234.07716200003</v>
-      </c>
-      <c r="G68" s="107">
-        <f>E68+F68</f>
-        <v>3643008.1799999997</v>
-      </c>
-      <c r="H68" s="142" t="str">
-        <f>IF(D68=G68, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I68" s="161">
-        <f>D68-G68</f>
-        <v>1479111.0600000005</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
+      <c r="D67" s="200"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="7"/>
+      <c r="H67" s="142"/>
+    </row>
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="200"/>
+      <c r="E68" s="112"/>
+      <c r="F68" s="7"/>
+      <c r="H68" s="142"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="B69" s="97"/>
       <c r="C69" s="7"/>
-      <c r="D69" s="166"/>
-      <c r="E69" s="113"/>
-      <c r="F69" s="7"/>
+      <c r="D69" s="199">
+        <v>117300</v>
+      </c>
+      <c r="E69" s="141">
+        <f>D69*91.91%</f>
+        <v>107810.43</v>
+      </c>
+      <c r="F69" s="129">
+        <f>D69*8.09%</f>
+        <v>9489.57</v>
+      </c>
+      <c r="G69" s="147"/>
       <c r="H69" s="142"/>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
-      <c r="D70" s="166"/>
-      <c r="E70" s="112"/>
+      <c r="D70" s="199"/>
+      <c r="E70" s="150">
+        <f>D70</f>
+        <v>0</v>
+      </c>
       <c r="F70" s="7"/>
       <c r="H70" s="142"/>
-    </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="166"/>
-      <c r="E71" s="112"/>
-      <c r="F71" s="7"/>
-      <c r="H71" s="142"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="93" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72" s="97"/>
+      <c r="I70" s="107"/>
+    </row>
+    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" s="94"/>
+      <c r="C71" s="94"/>
+      <c r="D71" s="197">
+        <f>SUM(D69:D70)</f>
+        <v>117300</v>
+      </c>
+      <c r="E71" s="106">
+        <f>SUM(E69:E70)</f>
+        <v>107810.43</v>
+      </c>
+      <c r="F71" s="106">
+        <f>SUM(F69:F70)</f>
+        <v>9489.57</v>
+      </c>
+      <c r="G71" s="107">
+        <f>E71+F71</f>
+        <v>117300</v>
+      </c>
+      <c r="H71" s="142" t="str">
+        <f>IF(D71=G71, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J71" s="107"/>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="173">
-        <v>117300</v>
-      </c>
-      <c r="E72" s="141">
-        <f>D72*91.91%</f>
-        <v>107810.43</v>
-      </c>
-      <c r="F72" s="129">
-        <f>D72*8.09%</f>
-        <v>9489.57</v>
-      </c>
-      <c r="G72" s="147"/>
+      <c r="D72" s="200"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="7"/>
       <c r="H72" s="142"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="111"/>
-      <c r="E73" s="150">
-        <f>D73</f>
-        <v>0</v>
-      </c>
+      <c r="D73" s="200"/>
+      <c r="E73" s="112"/>
       <c r="F73" s="7"/>
       <c r="H73" s="142"/>
-      <c r="I73" s="107"/>
-    </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="94" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" s="94"/>
-      <c r="C74" s="94"/>
-      <c r="D74" s="106">
-        <f>SUM(D72:D73)</f>
-        <v>117300</v>
-      </c>
-      <c r="E74" s="106">
-        <f>SUM(E72:E73)</f>
-        <v>107810.43</v>
-      </c>
-      <c r="F74" s="106">
-        <f>SUM(F72:F73)</f>
-        <v>9489.57</v>
-      </c>
-      <c r="G74" s="107">
-        <f>E74+F74</f>
-        <v>117300</v>
-      </c>
-      <c r="H74" s="142" t="str">
-        <f>IF(D74=G74, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J74" s="107"/>
-    </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="200"/>
+      <c r="E74" s="112"/>
+      <c r="F74" s="7"/>
+      <c r="H74" s="142"/>
+    </row>
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="C75" s="7"/>
-      <c r="D75" s="166"/>
-      <c r="E75" s="113"/>
-      <c r="F75" s="7"/>
+      <c r="D75" s="199">
+        <v>246000</v>
+      </c>
+      <c r="E75" s="141">
+        <f>D75*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F75" s="129">
+        <f>D75*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G75" t="s">
+        <v>139</v>
+      </c>
       <c r="H75" s="142"/>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="7"/>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="93" t="s">
+        <v>107</v>
+      </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="166"/>
-      <c r="E76" s="112"/>
-      <c r="F76" s="7"/>
+      <c r="D76" s="199">
+        <v>35000</v>
+      </c>
+      <c r="E76" s="141">
+        <f>D76*91.91%</f>
+        <v>32168.499999999996</v>
+      </c>
+      <c r="F76" s="129">
+        <f>D76*8.09%</f>
+        <v>2831.5</v>
+      </c>
       <c r="H76" s="142"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="93" t="s">
-        <v>13</v>
-      </c>
+      <c r="J76" s="111"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
-      <c r="D77" s="166"/>
-      <c r="E77" s="112"/>
+      <c r="D77" s="200"/>
+      <c r="E77" s="114"/>
       <c r="F77" s="7"/>
       <c r="H77" s="142"/>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="93" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="111">
-        <v>246000</v>
-      </c>
-      <c r="E78" s="141">
-        <f>D78*91.91%</f>
-        <v>226098.59999999998</v>
-      </c>
-      <c r="F78" s="129">
-        <f>D78*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G78" t="s">
-        <v>139</v>
-      </c>
-      <c r="H78" s="142"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J77" s="107"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" s="94"/>
+      <c r="C78" s="94"/>
+      <c r="D78" s="197">
+        <f>SUM(D75:D77)</f>
+        <v>281000</v>
+      </c>
+      <c r="E78" s="106">
+        <f>SUM(E75:E77)</f>
+        <v>258267.09999999998</v>
+      </c>
+      <c r="F78" s="106">
+        <f>SUM(F75:F77)</f>
+        <v>22732.9</v>
+      </c>
+      <c r="G78" s="107">
+        <f>E78+F78</f>
+        <v>281000</v>
+      </c>
+      <c r="H78" s="142" t="str">
+        <f>IF(D78=G78, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J78" s="107"/>
+    </row>
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="93" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="111">
-        <v>35000</v>
-      </c>
-      <c r="E79" s="141">
-        <f>D79*91.91%</f>
-        <v>32168.499999999996</v>
-      </c>
-      <c r="F79" s="129">
-        <f>D79*8.09%</f>
-        <v>2831.5</v>
-      </c>
+      <c r="D79" s="199"/>
+      <c r="E79" s="115"/>
+      <c r="F79" s="7"/>
       <c r="H79" s="142"/>
-      <c r="J79" s="111"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="7"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="93" t="s">
+        <v>101</v>
+      </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="166"/>
-      <c r="E80" s="114"/>
-      <c r="F80" s="7"/>
+      <c r="D80" s="199">
+        <v>134524.87</v>
+      </c>
+      <c r="E80" s="141">
+        <f>D80*91.91%</f>
+        <v>123641.80801699999</v>
+      </c>
+      <c r="F80" s="129">
+        <f>D80*8.09%</f>
+        <v>10883.061983</v>
+      </c>
       <c r="H80" s="142"/>
-      <c r="J80" s="107"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="94"/>
-      <c r="C81" s="94"/>
-      <c r="D81" s="106">
-        <f>SUM(D78:D80)</f>
-        <v>281000</v>
-      </c>
-      <c r="E81" s="106">
-        <f>SUM(E78:E80)</f>
-        <v>258267.09999999998</v>
-      </c>
-      <c r="F81" s="106">
-        <f>SUM(F78:F80)</f>
-        <v>22732.9</v>
-      </c>
-      <c r="G81" s="107">
-        <f>E81+F81</f>
-        <v>281000</v>
-      </c>
-      <c r="H81" s="142" t="str">
-        <f>IF(D81=G81, "", "Error")</f>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="120"/>
+      <c r="D81" s="199">
+        <v>44400</v>
+      </c>
+      <c r="E81" s="141">
+        <f>D81*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F81" s="129">
+        <f>D81*8.09%</f>
+        <v>3591.96</v>
+      </c>
+      <c r="H81" s="142"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" s="94"/>
+      <c r="C82" s="94"/>
+      <c r="D82" s="145">
+        <f>SUM(D80:D81)</f>
+        <v>178924.87</v>
+      </c>
+      <c r="E82" s="139">
+        <f t="shared" ref="E82:F82" si="17">SUM(E80:E81)</f>
+        <v>164449.84801699998</v>
+      </c>
+      <c r="F82" s="139">
+        <f t="shared" si="17"/>
+        <v>14475.021982999999</v>
+      </c>
+      <c r="G82" s="107">
+        <f>E82+F82</f>
+        <v>178924.87</v>
+      </c>
+      <c r="H82" s="142" t="str">
+        <f>IF(D82=G82, "", "Error")</f>
         <v/>
       </c>
-      <c r="J81" s="107"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="93" t="s">
-        <v>100</v>
-      </c>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="111"/>
-      <c r="E82" s="115"/>
-      <c r="F82" s="7"/>
-      <c r="H82" s="142"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="93" t="s">
-        <v>101</v>
-      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="111">
-        <f>155582.25+151.2+3552+9324+348.88+1800</f>
-        <v>170758.33000000002</v>
-      </c>
-      <c r="E83" s="141">
-        <f>D83*91.91%</f>
-        <v>156943.981103</v>
-      </c>
-      <c r="F83" s="129">
-        <f>D83*8.09%</f>
-        <v>13814.348897000002</v>
-      </c>
+      <c r="D83" s="164"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="7"/>
       <c r="H83" s="142"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="120"/>
-      <c r="D84" s="111">
-        <v>44400</v>
-      </c>
-      <c r="E84" s="141">
+    <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="98" t="s">
+        <v>133</v>
+      </c>
+      <c r="B84" s="98"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="165"/>
+      <c r="E84" s="116">
         <f>D84*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F84" s="129">
+        <v>0</v>
+      </c>
+      <c r="F84" s="131">
         <f>D84*8.09%</f>
-        <v>3591.96</v>
-      </c>
-      <c r="H84" s="142"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" s="94"/>
-      <c r="C85" s="94"/>
-      <c r="D85" s="145">
-        <f>SUM(D83:D84)</f>
-        <v>215158.33000000002</v>
-      </c>
-      <c r="E85" s="139">
-        <f t="shared" ref="E85:F85" si="17">SUM(E83:E84)</f>
-        <v>197752.02110299998</v>
-      </c>
-      <c r="F85" s="139">
-        <f t="shared" si="17"/>
-        <v>17406.308897000003</v>
-      </c>
-      <c r="G85" s="107">
-        <f>E85+F85</f>
-        <v>215158.33</v>
-      </c>
-      <c r="H85" s="142" t="str">
-        <f>IF(D85=G85, "", "Error")</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="107">
+        <f>E84+F84</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="142" t="str">
+        <f>IF(D84=G84, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="167"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="7"/>
-      <c r="H86" s="142"/>
-    </row>
-    <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98" t="s">
-        <v>133</v>
-      </c>
-      <c r="B87" s="98"/>
-      <c r="C87" s="98"/>
-      <c r="D87" s="168">
-        <f>7000000-6426943.64</f>
-        <v>573056.36000000034</v>
-      </c>
-      <c r="E87" s="116">
-        <f>D87*91.91%</f>
-        <v>526696.10047600023</v>
-      </c>
-      <c r="F87" s="131">
-        <f>D87*8.09%</f>
-        <v>46360.25952400003</v>
-      </c>
-      <c r="G87" s="107">
-        <f>E87+F87</f>
-        <v>573056.36000000022</v>
-      </c>
-      <c r="H87" s="142" t="str">
-        <f>IF(D87=G87, "", "Error")</f>
+    <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1"/>
+      <c r="D85" s="163"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="144"/>
+      <c r="H85" s="142"/>
+    </row>
+    <row r="86" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="59"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="166">
+        <f>SUM(D84+D82+D78+D71+D65+D49+D32+D27+D44)</f>
+        <v>7679928.3599999994</v>
+      </c>
+      <c r="E86" s="140">
+        <f>SUM(E84+E82+E78+E71+E65+E49+E32+E27+E44)</f>
+        <v>7243574.8538659997</v>
+      </c>
+      <c r="F86" s="140">
+        <f>SUM(F84+F82+F78+F71+F65+F49+F32+F27+F44)</f>
+        <v>436353.50613400002</v>
+      </c>
+      <c r="G86" s="107">
+        <f>E86+F86</f>
+        <v>7679928.3599999994</v>
+      </c>
+      <c r="H86" s="142" t="str">
+        <f>IF(D86=G86, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="1"/>
-      <c r="D88" s="165"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="144"/>
-      <c r="H88" s="142"/>
-    </row>
-    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B89" s="59"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="169">
-        <f>SUM(D87+D85+D81+D74+D68+D49+D32+D27+D44)</f>
-        <v>8184667.3900000006</v>
-      </c>
-      <c r="E89" s="140">
-        <f>SUM(E87+E85+E81+E74+E68+E49+E32+E27+E44)</f>
-        <v>6222562.1075030006</v>
-      </c>
-      <c r="F89" s="140">
-        <f>SUM(F87+F85+F81+F74+F68+F49+F32+F27+F44)</f>
-        <v>482994.22249700007</v>
-      </c>
-      <c r="G89" s="107">
-        <f>E89+F89</f>
-        <v>6705556.330000001</v>
-      </c>
-      <c r="H89" s="142" t="str">
-        <f>IF(D89=G89, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I89" s="161">
-        <f>D89-G89</f>
-        <v>1479111.0599999996</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D90" s="165"/>
+      <c r="I86" s="161">
+        <f>D86-G86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D87" s="163"/>
+      <c r="E87" s="107"/>
+    </row>
+    <row r="88" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="172" t="s">
+        <v>152</v>
+      </c>
+      <c r="B88" s="136"/>
+      <c r="C88" s="136"/>
+      <c r="E88" s="107"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+      <c r="C89" s="134"/>
+      <c r="E89" s="107"/>
+    </row>
+    <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="C90" s="134"/>
       <c r="E90" s="107"/>
     </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="175" t="s">
-        <v>152</v>
-      </c>
-      <c r="B91" s="136"/>
-      <c r="C91" s="136"/>
+    <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B91" s="138"/>
+      <c r="C91" s="135">
+        <f>SUM(C89:C90)</f>
+        <v>0</v>
+      </c>
       <c r="E91" s="107"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="C92" s="134"/>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E92" s="107"/>
     </row>
-    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="1"/>
-      <c r="C93" s="134"/>
-      <c r="E93" s="107"/>
-    </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="137" t="s">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E93" s="132"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="220" t="s">
+        <v>113</v>
+      </c>
+      <c r="B94" s="221"/>
+      <c r="C94" s="221"/>
+      <c r="D94" s="221"/>
+      <c r="E94" s="156" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" s="157" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="217"/>
+      <c r="B95" s="218"/>
+      <c r="C95" s="219"/>
+      <c r="D95" s="111"/>
+      <c r="E95" s="141">
+        <f t="shared" ref="E95:E96" si="18">D95*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="129">
+        <f t="shared" ref="F95:F96" si="19">D95*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="225"/>
+      <c r="B96" s="226"/>
+      <c r="C96" s="227"/>
+      <c r="D96" s="111"/>
+      <c r="E96" s="141">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="129">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="B94" s="138"/>
-      <c r="C94" s="135">
-        <f>SUM(C92:C93)</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="107"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E95" s="107"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E96" s="132"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" s="216" t="s">
-        <v>113</v>
-      </c>
-      <c r="B97" s="217"/>
-      <c r="C97" s="217"/>
-      <c r="D97" s="217"/>
-      <c r="E97" s="156" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" s="157" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="213" t="s">
-        <v>164</v>
-      </c>
-      <c r="B98" s="214"/>
-      <c r="C98" s="215"/>
-      <c r="D98" s="111">
-        <v>2900000</v>
-      </c>
-      <c r="E98" s="141">
-        <f t="shared" ref="E98:E99" si="18">D98*91.91%</f>
-        <v>2665389.9999999995</v>
-      </c>
-      <c r="F98" s="129">
-        <f t="shared" ref="F98:F99" si="19">D98*8.09%</f>
-        <v>234610</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="221"/>
-      <c r="B99" s="222"/>
-      <c r="C99" s="223"/>
-      <c r="D99" s="111"/>
-      <c r="E99" s="141">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F99" s="129">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="210" t="s">
+      <c r="B97" s="215"/>
+      <c r="C97" s="216"/>
+      <c r="D97" s="155">
+        <f>SUM(D95:D96)</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="155">
+        <f>SUM(E95:E96)</f>
+        <v>0</v>
+      </c>
+      <c r="F97" s="155">
+        <f>SUM(F95:F96)</f>
+        <v>0</v>
+      </c>
+      <c r="H97" s="107">
+        <f>E97+F97</f>
+        <v>0</v>
+      </c>
+      <c r="I97" s="142" t="str">
+        <f>IF(D97=H97, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="107"/>
+    </row>
+    <row r="100" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="101" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" s="102">
+        <f>D86</f>
+        <v>7679928.3599999994</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" s="104">
+        <f>D86-D84</f>
+        <v>7679928.3599999994</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D102" s="204"/>
+      <c r="E102" s="204"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B103" s="74"/>
+      <c r="C103" s="75"/>
+      <c r="D103" s="204"/>
+      <c r="E103" s="204"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="B104" s="10">
+        <v>807261.99494061619</v>
+      </c>
+      <c r="C104" s="77"/>
+      <c r="D104" s="204"/>
+      <c r="E104" s="204"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="B105" s="91">
+        <f>PRORRATEO!G52</f>
+        <v>9627966.0681870002</v>
+      </c>
+      <c r="C105" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="D105" s="204"/>
+      <c r="E105" s="204"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="78" t="s">
+        <v>115</v>
+      </c>
+      <c r="B106" s="158">
+        <f>-B101</f>
+        <v>-7679928.3599999994</v>
+      </c>
+      <c r="C106" s="75"/>
+      <c r="D106" s="204"/>
+      <c r="E106" s="204"/>
+      <c r="G106" s="111"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" s="158">
+        <f>-D97</f>
+        <v>0</v>
+      </c>
+      <c r="C107" s="75"/>
+      <c r="D107" s="204"/>
+      <c r="E107" s="204"/>
+      <c r="G107" s="121"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="B108" s="158">
+        <f>-B115</f>
+        <v>-20000</v>
+      </c>
+      <c r="C108" s="79"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="78" t="s">
+        <v>120</v>
+      </c>
+      <c r="B109" s="92">
+        <f>-C91</f>
+        <v>0</v>
+      </c>
+      <c r="C109" s="79"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="78"/>
+      <c r="B110" s="74"/>
+      <c r="C110" s="143"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="B111" s="80">
+        <f>SUM(B104:B110)</f>
+        <v>2735299.703127617</v>
+      </c>
+      <c r="C111" s="143"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="79"/>
+      <c r="C112" s="75"/>
+      <c r="D112" s="82"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C113" s="75"/>
+      <c r="D113" s="107"/>
+      <c r="E113" s="161"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="B114" s="178">
+        <v>-212694.54000000004</v>
+      </c>
+      <c r="C114" s="81"/>
+      <c r="D114" s="161"/>
+      <c r="E114" s="161"/>
+      <c r="F114" s="161"/>
+    </row>
+    <row r="115" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="B115" s="92">
+        <v>20000</v>
+      </c>
+      <c r="C115" s="81"/>
+      <c r="D115" s="161"/>
+      <c r="E115" s="168"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="76"/>
+      <c r="B116" s="158"/>
+      <c r="C116" s="81"/>
+      <c r="E116" s="107"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="76"/>
+      <c r="B117" s="158"/>
+      <c r="C117" s="81"/>
+      <c r="E117" s="107"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B100" s="211"/>
-      <c r="C100" s="212"/>
-      <c r="D100" s="155">
-        <f>SUM(D98:D99)</f>
-        <v>2900000</v>
-      </c>
-      <c r="E100" s="155">
-        <f>SUM(E98:E99)</f>
-        <v>2665389.9999999995</v>
-      </c>
-      <c r="F100" s="155">
-        <f>SUM(F98:F99)</f>
-        <v>234610</v>
-      </c>
-      <c r="H100" s="107">
-        <f>E100+F100</f>
-        <v>2899999.9999999995</v>
-      </c>
-      <c r="I100" s="142" t="str">
-        <f>IF(D100=H100, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E102" s="107"/>
-    </row>
-    <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="101" t="s">
-        <v>104</v>
-      </c>
-      <c r="B103" s="102">
-        <f>D89</f>
-        <v>8184667.3900000006</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="103" t="s">
-        <v>106</v>
-      </c>
-      <c r="B104" s="104">
-        <f>D89-D87</f>
-        <v>7611611.0300000003</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D105" s="200"/>
-      <c r="E105" s="200"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="B106" s="74"/>
-      <c r="C106" s="75"/>
-      <c r="D106" s="200"/>
-      <c r="E106" s="200"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="76" t="s">
-        <v>91</v>
-      </c>
-      <c r="B107" s="10">
-        <v>3617497.2979896166</v>
-      </c>
-      <c r="C107" s="77"/>
-      <c r="D107" s="200"/>
-      <c r="E107" s="200"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="B108" s="91">
-        <f>PRORRATEO!G52</f>
-        <v>6941937.3369510006</v>
-      </c>
-      <c r="C108" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="D108" s="200"/>
-      <c r="E108" s="200"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="78" t="s">
-        <v>115</v>
-      </c>
-      <c r="B109" s="158">
-        <f>-B104</f>
-        <v>-7611611.0300000003</v>
-      </c>
-      <c r="C109" s="75"/>
-      <c r="D109" s="200"/>
-      <c r="E109" s="200"/>
-      <c r="G109" s="111"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="78" t="s">
-        <v>114</v>
-      </c>
-      <c r="B110" s="158">
-        <f>-D100</f>
-        <v>-2900000</v>
-      </c>
-      <c r="C110" s="75"/>
-      <c r="D110" s="200"/>
-      <c r="E110" s="200"/>
-      <c r="G110" s="121"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="78" t="s">
-        <v>165</v>
-      </c>
-      <c r="B111" s="158">
-        <f>-77229-250000</f>
-        <v>-327229</v>
-      </c>
-      <c r="C111" s="75"/>
-      <c r="D111" s="182"/>
-      <c r="E111" s="182"/>
-      <c r="G111" s="121"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="78" t="s">
-        <v>166</v>
-      </c>
-      <c r="B112" s="158">
-        <f>-19000*2</f>
-        <v>-38000</v>
-      </c>
-      <c r="C112" s="75"/>
-      <c r="D112" s="182"/>
-      <c r="E112" s="182"/>
-      <c r="G112" s="121"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="78" t="s">
-        <v>105</v>
-      </c>
-      <c r="B113" s="158">
-        <f>-B120</f>
-        <v>-60000</v>
-      </c>
-      <c r="C113" s="79"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A114" s="78" t="s">
-        <v>120</v>
-      </c>
-      <c r="B114" s="92">
-        <f>-C94</f>
-        <v>0</v>
-      </c>
-      <c r="C114" s="79"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="78"/>
-      <c r="B115" s="74"/>
-      <c r="C115" s="143"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="76" t="s">
-        <v>94</v>
-      </c>
-      <c r="B116" s="80">
-        <f>SUM(B107:B115)</f>
-        <v>-377405.39505938347</v>
-      </c>
-      <c r="C116" s="143"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="79"/>
-      <c r="C117" s="75"/>
-      <c r="D117" s="82"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C118" s="75"/>
-      <c r="D118" s="107"/>
-      <c r="E118" s="161"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="B119" s="184">
-        <v>-272694.54000000004</v>
-      </c>
-      <c r="C119" s="81"/>
+      <c r="B118" s="100">
+        <f>SUM(B114:B117)</f>
+        <v>-192694.54000000004</v>
+      </c>
+      <c r="C118" s="81"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C119" s="82"/>
       <c r="D119" s="161"/>
-      <c r="E119" s="161"/>
-      <c r="F119" s="161"/>
-    </row>
-    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="B120" s="92">
-        <v>60000</v>
-      </c>
-      <c r="C120" s="81"/>
-      <c r="D120" s="161"/>
-      <c r="E120" s="171"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121" s="76"/>
-      <c r="B121" s="158"/>
-      <c r="C121" s="81"/>
-      <c r="E121" s="107"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="76"/>
-      <c r="B122" s="158"/>
-      <c r="C122" s="81"/>
-      <c r="E122" s="107"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A123" s="99" t="s">
-        <v>29</v>
-      </c>
-      <c r="B123" s="100">
-        <f>SUM(B119:B122)</f>
-        <v>-212694.54000000004</v>
-      </c>
-      <c r="C123" s="81"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C124" s="82"/>
-      <c r="D124" s="161"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B125" s="79"/>
-      <c r="C125" s="75"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N127" s="11"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B130" s="199"/>
-      <c r="C130" s="199"/>
-      <c r="D130" s="199"/>
-      <c r="E130" s="199"/>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B131" s="199"/>
-      <c r="C131" s="199"/>
-      <c r="D131" s="199"/>
-      <c r="E131" s="199"/>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B132" s="199"/>
-      <c r="C132" s="199"/>
-      <c r="D132" s="199"/>
-      <c r="E132" s="199"/>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B133" s="199"/>
-      <c r="C133" s="199"/>
-      <c r="D133" s="199"/>
-      <c r="E133" s="199"/>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B134" s="199"/>
-      <c r="C134" s="199"/>
-      <c r="D134" s="199"/>
-      <c r="E134" s="199"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B120" s="79"/>
+      <c r="C120" s="75"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N122" s="11"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B125" s="203"/>
+      <c r="C125" s="203"/>
+      <c r="D125" s="203"/>
+      <c r="E125" s="203"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B126" s="203"/>
+      <c r="C126" s="203"/>
+      <c r="D126" s="203"/>
+      <c r="E126" s="203"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B127" s="203"/>
+      <c r="C127" s="203"/>
+      <c r="D127" s="203"/>
+      <c r="E127" s="203"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B128" s="203"/>
+      <c r="C128" s="203"/>
+      <c r="D128" s="203"/>
+      <c r="E128" s="203"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" s="203"/>
+      <c r="C129" s="203"/>
+      <c r="D129" s="203"/>
+      <c r="E129" s="203"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B130:E134"/>
-    <mergeCell ref="D105:E110"/>
+  <mergeCells count="11">
+    <mergeCell ref="B125:E129"/>
+    <mergeCell ref="D102:E107"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A53:C53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4003,185 +3907,184 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="238" t="s">
-        <v>167</v>
-      </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="240"/>
-      <c r="K1" s="188" t="s">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="245" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="247"/>
+      <c r="K1" s="182" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="227">
-        <f>RESUMEN!D89</f>
-        <v>8184667.3900000006</v>
-      </c>
-      <c r="M1" s="228"/>
-      <c r="N1" s="189"/>
+      <c r="L1" s="232">
+        <f>RESUMEN!D86</f>
+        <v>7679928.3599999994</v>
+      </c>
+      <c r="M1" s="233"/>
+      <c r="N1" s="183"/>
       <c r="O1" s="130">
         <f>L1*8.09%</f>
-        <v>662139.59185100009</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="241"/>
-      <c r="B2" s="242"/>
-      <c r="C2" s="242"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="190" t="s">
+        <v>621306.20432399993</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="248"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="249"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="250"/>
+      <c r="K2" s="184" t="s">
         <v>125</v>
       </c>
       <c r="L2" s="8"/>
-      <c r="M2" s="191">
+      <c r="M2" s="185">
         <v>7000000</v>
       </c>
-      <c r="N2" s="192"/>
+      <c r="N2" s="186"/>
       <c r="O2" s="130">
         <f>O1-K7-553-50-86-8</f>
-        <v>143486.29366400006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="241"/>
-      <c r="B3" s="242"/>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="242"/>
-      <c r="I3" s="242"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="190" t="s">
+        <v>184255.69818999991</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="248"/>
+      <c r="B3" s="249"/>
+      <c r="C3" s="249"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="249"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="250"/>
+      <c r="K3" s="184" t="s">
         <v>131</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="193">
-        <f>RESUMEN!D100</f>
-        <v>2900000</v>
-      </c>
-      <c r="N3" s="194"/>
+      <c r="M3" s="187">
+        <f>RESUMEN!D97</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="188"/>
       <c r="O3" s="72"/>
     </row>
-    <row r="4" spans="1:16" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="244"/>
-      <c r="B4" s="245"/>
-      <c r="C4" s="245"/>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="195" t="s">
+    <row r="4" spans="1:16" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="251"/>
+      <c r="B4" s="252"/>
+      <c r="C4" s="252"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="189" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="196"/>
-      <c r="M4" s="197">
-        <f>O4</f>
+      <c r="L4" s="190"/>
+      <c r="M4" s="191">
         <v>966666.66666666663</v>
       </c>
-      <c r="N4" s="198"/>
+      <c r="N4" s="192"/>
       <c r="O4" s="130">
         <f>M3/3</f>
-        <v>966666.66666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="224" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="236" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="247" t="s">
+      <c r="B5" s="254" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="224" t="s">
+      <c r="C5" s="236" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="236" t="s">
+      <c r="D5" s="243" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="224" t="s">
+      <c r="E5" s="236" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="224" t="s">
+      <c r="F5" s="236" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="224" t="s">
+      <c r="G5" s="236" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="231" t="s">
+      <c r="H5" s="238" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="236" t="s">
+      <c r="I5" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="229" t="s">
+      <c r="J5" s="234" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="229" t="s">
+      <c r="K5" s="234" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="234" t="s">
+      <c r="L5" s="241" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="229" t="s">
+      <c r="M5" s="234" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="229" t="s">
+      <c r="N5" s="234" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="225"/>
-      <c r="B6" s="248"/>
-      <c r="C6" s="225"/>
-      <c r="D6" s="249"/>
-      <c r="E6" s="225"/>
-      <c r="F6" s="225"/>
-      <c r="G6" s="225"/>
-      <c r="H6" s="232"/>
-      <c r="I6" s="237"/>
-      <c r="J6" s="230"/>
-      <c r="K6" s="233"/>
-      <c r="L6" s="235"/>
-      <c r="M6" s="233"/>
-      <c r="N6" s="230"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="237"/>
+      <c r="B6" s="255"/>
+      <c r="C6" s="237"/>
+      <c r="D6" s="256"/>
+      <c r="E6" s="237"/>
+      <c r="F6" s="237"/>
+      <c r="G6" s="237"/>
+      <c r="H6" s="239"/>
+      <c r="I6" s="244"/>
+      <c r="J6" s="235"/>
+      <c r="K6" s="240"/>
+      <c r="L6" s="242"/>
+      <c r="M6" s="240"/>
+      <c r="N6" s="235"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4196,37 +4099,36 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="87">
-        <v>524871.62695100007</v>
-      </c>
-      <c r="G7" s="180">
-        <f>F7</f>
-        <v>524871.62695100007</v>
+        <v>596159.63152033335</v>
+      </c>
+      <c r="G7" s="201">
+        <f>F7-60</f>
+        <v>596099.63152033335</v>
       </c>
       <c r="H7" s="126">
         <f>F7-G7</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" s="105">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J7" s="87">
-        <f>234610/3</f>
-        <v>78203.333333333328</v>
+        <v>0</v>
       </c>
       <c r="K7" s="87">
-        <v>517956.29818700004</v>
+        <v>436353.50613400002</v>
       </c>
       <c r="L7" s="97"/>
       <c r="M7" s="6">
         <f>K7+J7+H7+L7</f>
-        <v>596159.63152033335</v>
+        <v>436413.50613400002</v>
       </c>
       <c r="N7" s="10">
         <f>M7*6% + M7</f>
-        <v>631929.20941155334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>462598.31650204002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4241,17 +4143,17 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="87">
-        <v>164206.27016451582</v>
-      </c>
-      <c r="G8" s="180">
-        <v>165000</v>
+        <v>175269.60349784917</v>
+      </c>
+      <c r="G8" s="201">
+        <v>176000</v>
       </c>
       <c r="H8" s="126">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-793.72983548417687</v>
+        <v>-730.39650215083384</v>
       </c>
       <c r="I8" s="105">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" s="87">
         <f>M$4*E8%</f>
@@ -4261,17 +4163,17 @@
         <f>M$2*E8 /100</f>
         <v>154700</v>
       </c>
-      <c r="L8" s="186"/>
+      <c r="L8" s="180"/>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>175269.60349784917</v>
+        <v>175332.93683118251</v>
       </c>
       <c r="N8" s="10">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>185785.77970772012</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>185852.91304105346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4286,18 +4188,18 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="87">
-        <v>333645.26953426329</v>
-      </c>
-      <c r="G9" s="181">
-        <f>373875-G34</f>
-        <v>333645</v>
+        <v>345396.93620092998</v>
+      </c>
+      <c r="G9" s="202">
+        <f>388417-G34</f>
+        <v>345397</v>
       </c>
       <c r="H9" s="126">
         <f t="shared" si="0"/>
-        <v>0.26953426329419017</v>
+        <v>-6.3799070019740611E-2</v>
       </c>
       <c r="I9" s="105">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J9" s="87">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
@@ -4307,19 +4209,17 @@
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>294700</v>
       </c>
-      <c r="L9" s="186">
-        <v>10000</v>
-      </c>
+      <c r="L9" s="180"/>
       <c r="M9" s="6">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>345396.93620092998</v>
+        <v>335396.60286759667</v>
       </c>
       <c r="N9" s="10">
         <f t="shared" si="1"/>
-        <v>366120.75237298576</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>355520.39903965249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4334,18 +4234,18 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="87">
-        <v>211580</v>
-      </c>
-      <c r="G10" s="180">
+        <v>226253.33333333334</v>
+      </c>
+      <c r="G10" s="201">
         <f>F10</f>
-        <v>211580</v>
+        <v>226253.33333333334</v>
       </c>
       <c r="H10" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I10" s="105">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J10" s="87">
         <f t="shared" si="2"/>
@@ -4355,7 +4255,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L10" s="186"/>
+      <c r="L10" s="180"/>
       <c r="M10" s="6">
         <f t="shared" si="4"/>
         <v>226253.33333333334</v>
@@ -4365,7 +4265,7 @@
         <v>239828.53333333335</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4380,18 +4280,18 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="87">
-        <v>255535</v>
-      </c>
-      <c r="G11" s="180">
+        <v>273256.66666666669</v>
+      </c>
+      <c r="G11" s="201">
         <f>F11</f>
-        <v>255535</v>
+        <v>273256.66666666669</v>
       </c>
       <c r="H11" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="105">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J11" s="87">
         <f t="shared" si="2"/>
@@ -4401,7 +4301,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L11" s="186"/>
+      <c r="L11" s="180"/>
       <c r="M11" s="6">
         <f t="shared" si="4"/>
         <v>273256.66666666669</v>
@@ -4412,7 +4312,7 @@
       </c>
       <c r="P11" s="107"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4427,18 +4327,18 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="87">
-        <v>211580</v>
-      </c>
-      <c r="G12" s="181">
+        <v>226253.33333333334</v>
+      </c>
+      <c r="G12" s="202">
         <f>F12</f>
-        <v>211580</v>
+        <v>226253.33333333334</v>
       </c>
       <c r="H12" s="126">
         <f>F12-G12</f>
         <v>0</v>
       </c>
       <c r="I12" s="105">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J12" s="87">
         <f t="shared" si="2"/>
@@ -4448,7 +4348,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L12" s="186"/>
+      <c r="L12" s="180"/>
       <c r="M12" s="6">
         <f t="shared" si="4"/>
         <v>226253.33333333334</v>
@@ -4458,7 +4358,7 @@
         <v>239828.53333333335</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4473,18 +4373,18 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="87">
-        <v>343076.36741924175</v>
-      </c>
-      <c r="G13" s="181">
-        <f>309490-G50</f>
-        <v>265535</v>
+        <v>350798.03408590844</v>
+      </c>
+      <c r="G13" s="202">
+        <f>320260+RESUMEN!D60-G50</f>
+        <v>350798.21666666667</v>
       </c>
       <c r="H13" s="126">
         <f t="shared" si="0"/>
-        <v>77541.367419241753</v>
+        <v>-0.18258075823541731</v>
       </c>
       <c r="I13" s="105">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J13" s="87">
         <f t="shared" si="2"/>
@@ -4494,17 +4394,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L13" s="186"/>
+      <c r="L13" s="180"/>
       <c r="M13" s="6">
         <f t="shared" si="4"/>
-        <v>350798.03408590844</v>
+        <v>273256.48408590845</v>
       </c>
       <c r="N13" s="10">
         <f t="shared" si="1"/>
-        <v>371845.91613106296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>289651.87313106295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4519,17 +4419,17 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="87">
-        <v>224274.8</v>
-      </c>
-      <c r="G14" s="180">
-        <v>211580</v>
+        <v>248948.13333333333</v>
+      </c>
+      <c r="G14" s="201">
+        <v>263885</v>
       </c>
       <c r="H14" s="126">
         <f t="shared" si="0"/>
-        <v>12694.799999999988</v>
+        <v>-14936.866666666669</v>
       </c>
       <c r="I14" s="105">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J14" s="87">
         <f t="shared" si="2"/>
@@ -4539,19 +4439,17 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L14" s="186">
-        <v>10000</v>
-      </c>
+      <c r="L14" s="180"/>
       <c r="M14" s="6">
         <f t="shared" si="4"/>
-        <v>248948.13333333333</v>
+        <v>211316.46666666667</v>
       </c>
       <c r="N14" s="10">
         <f t="shared" si="1"/>
-        <v>263885.02133333334</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>223995.45466666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4566,18 +4464,18 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="87">
-        <v>255535.87099653395</v>
-      </c>
-      <c r="G15" s="181">
-        <f>292786-G35</f>
-        <v>255536</v>
+        <v>273256.53766320064</v>
+      </c>
+      <c r="G15" s="202">
+        <f>313090-G35</f>
+        <v>273256.66666666669</v>
       </c>
       <c r="H15" s="126">
         <f t="shared" si="0"/>
         <v>-0.12900346604874358</v>
       </c>
       <c r="I15" s="105">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J15" s="87">
         <f t="shared" si="2"/>
@@ -4587,7 +4485,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L15" s="186"/>
+      <c r="L15" s="180"/>
       <c r="M15" s="6">
         <f t="shared" si="4"/>
         <v>273256.53766320064</v>
@@ -4597,7 +4495,7 @@
         <v>289651.92992299265</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4612,18 +4510,18 @@
         <v>2.84</v>
       </c>
       <c r="F16" s="87">
-        <v>211579.62795000005</v>
-      </c>
-      <c r="G16" s="181">
-        <f>262969.71-G49</f>
-        <v>226464.71000000002</v>
+        <v>211368.25128333337</v>
+      </c>
+      <c r="G16" s="202">
+        <f>265429.22-G49</f>
+        <v>226392.55333333332</v>
       </c>
       <c r="H16" s="126">
         <f t="shared" si="0"/>
-        <v>-14885.082049999968</v>
+        <v>-15024.30204999994</v>
       </c>
       <c r="I16" s="105">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J16" s="87">
         <f t="shared" si="2"/>
@@ -4633,17 +4531,17 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L16" s="186"/>
+      <c r="L16" s="180"/>
       <c r="M16" s="6">
         <f t="shared" si="4"/>
-        <v>211368.25128333337</v>
+        <v>211229.0312833334</v>
       </c>
       <c r="N16" s="10">
         <f t="shared" si="1"/>
-        <v>224050.34636033338</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>223902.7731603334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4658,15 +4556,15 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="87">
-        <v>265534.97401111474</v>
-      </c>
-      <c r="G17" s="180">
-        <f>339290-G47-G48</f>
-        <v>265535</v>
+        <v>273256.64067778143</v>
+      </c>
+      <c r="G17" s="201">
+        <f>352127-G47-G48</f>
+        <v>273257</v>
       </c>
       <c r="H17" s="126">
         <f t="shared" si="0"/>
-        <v>-2.5988885259721428E-2</v>
+        <v>-0.35932221857365221</v>
       </c>
       <c r="I17" s="105">
         <v>12</v>
@@ -4679,17 +4577,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L17" s="186"/>
+      <c r="L17" s="180"/>
       <c r="M17" s="6">
         <f t="shared" si="4"/>
-        <v>273256.64067778143</v>
+        <v>273256.30734444811</v>
       </c>
       <c r="N17" s="10">
         <f t="shared" si="1"/>
-        <v>289652.03911844833</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>289651.685785115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -4704,18 +4602,18 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="87">
-        <v>210704.42713325133</v>
-      </c>
-      <c r="G18" s="180">
-        <f>260000-G51</f>
-        <v>217535</v>
+        <v>219422.76046658467</v>
+      </c>
+      <c r="G18" s="201">
+        <f>266000-G51</f>
+        <v>220590</v>
       </c>
       <c r="H18" s="126">
         <f t="shared" si="0"/>
-        <v>-6830.5728667486692</v>
+        <v>-1167.2395334153262</v>
       </c>
       <c r="I18" s="105">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18" s="87">
         <f t="shared" si="2"/>
@@ -4725,17 +4623,17 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L18" s="186"/>
+      <c r="L18" s="180"/>
       <c r="M18" s="6">
         <f t="shared" si="4"/>
-        <v>219422.76046658467</v>
+        <v>225086.09379991802</v>
       </c>
       <c r="N18" s="10">
         <f t="shared" si="1"/>
-        <v>232588.12609457975</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>238591.25942791309</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -4750,18 +4648,18 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="87">
-        <v>255535.48631516803</v>
-      </c>
-      <c r="G19" s="181">
-        <f>295765-G41</f>
-        <v>255535</v>
+        <v>273257.15298183472</v>
+      </c>
+      <c r="G19" s="202">
+        <f>316277-G41</f>
+        <v>273257</v>
       </c>
       <c r="H19" s="126">
         <f t="shared" si="0"/>
-        <v>0.48631516803288832</v>
+        <v>0.15298183471895754</v>
       </c>
       <c r="I19" s="105">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J19" s="87">
         <f t="shared" si="2"/>
@@ -4771,17 +4669,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L19" s="186"/>
+      <c r="L19" s="180"/>
       <c r="M19" s="6">
         <f t="shared" si="4"/>
-        <v>273257.15298183472</v>
+        <v>273256.81964850141</v>
       </c>
       <c r="N19" s="10">
         <f t="shared" si="1"/>
-        <v>289652.58216074482</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>289652.22882741148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -4796,18 +4694,18 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="87">
-        <v>211579.65585707471</v>
-      </c>
-      <c r="G20" s="180">
-        <f>248085-G38</f>
-        <v>211580</v>
+        <v>226252.98919040806</v>
+      </c>
+      <c r="G20" s="201">
+        <f>265290-G38</f>
+        <v>226253.33333333334</v>
       </c>
       <c r="H20" s="126">
         <f t="shared" si="0"/>
         <v>-0.34414292528526857</v>
       </c>
       <c r="I20" s="105">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J20" s="87">
         <f t="shared" si="2"/>
@@ -4817,7 +4715,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L20" s="186"/>
+      <c r="L20" s="180"/>
       <c r="M20" s="6">
         <f t="shared" si="4"/>
         <v>226252.98919040806</v>
@@ -4827,7 +4725,7 @@
         <v>239828.16854183254</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4842,18 +4740,18 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="87">
-        <v>255534.8886417959</v>
-      </c>
-      <c r="G21" s="180">
-        <f>295765-G45</f>
-        <v>255535</v>
+        <v>273256.55530846259</v>
+      </c>
+      <c r="G21" s="201">
+        <f>316277-G45</f>
+        <v>273257</v>
       </c>
       <c r="H21" s="126">
         <f t="shared" si="0"/>
-        <v>-0.11135820409981534</v>
+        <v>-0.44469153741374612</v>
       </c>
       <c r="I21" s="105">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21" s="87">
         <f t="shared" si="2"/>
@@ -4863,17 +4761,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L21" s="186"/>
+      <c r="L21" s="180"/>
       <c r="M21" s="6">
         <f t="shared" si="4"/>
-        <v>273256.55530846259</v>
+        <v>273256.22197512927</v>
       </c>
       <c r="N21" s="10">
         <f t="shared" si="1"/>
-        <v>289651.94862697035</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>289651.59529363702</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -4888,18 +4786,18 @@
         <v>2.84</v>
       </c>
       <c r="F22" s="87">
-        <v>211580</v>
-      </c>
-      <c r="G22" s="180">
+        <v>226253.33333333334</v>
+      </c>
+      <c r="G22" s="201">
         <f>F22</f>
-        <v>211580</v>
+        <v>226253.33333333334</v>
       </c>
       <c r="H22" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="87">
         <f t="shared" si="2"/>
@@ -4909,7 +4807,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L22" s="186"/>
+      <c r="L22" s="180"/>
       <c r="M22" s="6">
         <f t="shared" si="4"/>
         <v>226253.33333333334</v>
@@ -4919,7 +4817,7 @@
         <v>239828.53333333335</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -4934,18 +4832,18 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="87">
-        <v>320475.29717285704</v>
-      </c>
-      <c r="G23" s="181">
-        <f>361000-G46</f>
-        <v>323750</v>
+        <v>286180.88166989514</v>
+      </c>
+      <c r="G23" s="202">
+        <f>270000+40000-G46</f>
+        <v>267776.66666666669</v>
       </c>
       <c r="H23" s="126">
         <f t="shared" si="0"/>
-        <v>-3274.702827142959</v>
+        <v>18404.215003228455</v>
       </c>
       <c r="I23" s="105">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J23" s="87">
         <f t="shared" si="2"/>
@@ -4955,17 +4853,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L23" s="186"/>
+      <c r="L23" s="180"/>
       <c r="M23" s="6">
         <f t="shared" si="4"/>
-        <v>269981.96383952373</v>
+        <v>291660.88166989514</v>
       </c>
       <c r="N23" s="10">
         <f t="shared" si="1"/>
-        <v>286180.88166989514</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>309160.53457008884</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -4980,18 +4878,18 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="87">
-        <v>221580.37342107471</v>
-      </c>
-      <c r="G24" s="180">
-        <f>259000-G37</f>
-        <v>222495</v>
+        <v>225338.70675440805</v>
+      </c>
+      <c r="G24" s="201">
+        <f>259000+11000-G37</f>
+        <v>230963.33333333334</v>
       </c>
       <c r="H24" s="126">
         <f t="shared" si="0"/>
-        <v>-914.62657892529387</v>
+        <v>-5624.6265789252939</v>
       </c>
       <c r="I24" s="162">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J24" s="87">
         <f t="shared" si="2"/>
@@ -5001,17 +4899,19 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L24" s="186"/>
+      <c r="L24" s="180">
+        <v>10000</v>
+      </c>
       <c r="M24" s="6">
         <f t="shared" si="4"/>
-        <v>225338.70675440805</v>
+        <v>230628.70675440805</v>
       </c>
       <c r="N24" s="10">
         <f t="shared" si="1"/>
-        <v>238859.02915967253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>244466.42915967252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -5026,15 +4926,15 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="87">
-        <v>255535</v>
-      </c>
-      <c r="G25" s="180">
-        <f>F25</f>
-        <v>255535</v>
+        <v>1458255.6666666667</v>
+      </c>
+      <c r="G25" s="202">
+        <f>273257+2384999</f>
+        <v>2658256</v>
       </c>
       <c r="H25" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1200000.3333333333</v>
       </c>
       <c r="I25" s="105">
         <v>11</v>
@@ -5047,23 +4947,22 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L25" s="187">
-        <f>77229+250000+38000+(((K25+J25)*0.5))*6</f>
-        <v>1184999</v>
+      <c r="L25" s="181">
+        <v>1200000</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" si="4"/>
-        <v>1458255.6666666667</v>
+        <v>273256.33333333349</v>
       </c>
       <c r="N25" s="10">
         <f t="shared" si="1"/>
-        <v>1545751.0066666668</v>
+        <v>289651.71333333349</v>
       </c>
       <c r="P25" s="133"/>
       <c r="Q25" s="133"/>
       <c r="R25" s="133"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -5078,18 +4977,18 @@
         <v>6</v>
       </c>
       <c r="F26" s="87">
-        <v>-434833.00733396295</v>
-      </c>
-      <c r="G26" s="181">
-        <f>-G36-G30-G31</f>
-        <v>-118455</v>
+        <v>161621.99266603705</v>
+      </c>
+      <c r="G26" s="202">
+        <f>400000-G36-G30-G31</f>
+        <v>273330</v>
       </c>
       <c r="H26" s="127">
         <f t="shared" si="0"/>
-        <v>-316378.00733396295</v>
+        <v>-111708.00733396295</v>
       </c>
       <c r="I26" s="105">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J26" s="87">
         <f t="shared" si="2"/>
@@ -5099,17 +4998,17 @@
         <f t="shared" si="3"/>
         <v>420000</v>
       </c>
-      <c r="L26" s="186"/>
+      <c r="L26" s="180"/>
       <c r="M26" s="6">
         <f t="shared" si="4"/>
-        <v>161621.99266603705</v>
+        <v>366291.99266603705</v>
       </c>
       <c r="N26" s="10">
         <f t="shared" si="1"/>
-        <v>171319.31222599928</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>388269.51222599926</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5124,18 +5023,18 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="87">
-        <v>438805.37128526543</v>
-      </c>
-      <c r="G27" s="180">
-        <f>520005-G39-G40</f>
-        <v>433585</v>
+        <v>474457.03795193206</v>
+      </c>
+      <c r="G27" s="201">
+        <f>567000-G39-G40</f>
+        <v>474586.66666666669</v>
       </c>
       <c r="H27" s="126">
         <f t="shared" si="0"/>
-        <v>5220.371285265428</v>
+        <v>-129.62871473463019</v>
       </c>
       <c r="I27" s="105">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="87">
         <f t="shared" si="2"/>
@@ -5145,18 +5044,18 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L27" s="186"/>
+      <c r="L27" s="180"/>
       <c r="M27" s="6">
         <f t="shared" si="4"/>
-        <v>474457.03795193206</v>
+        <v>469107.037951932</v>
       </c>
       <c r="N27" s="10">
         <f t="shared" si="1"/>
-        <v>502924.46022904798</v>
+        <v>497253.46022904792</v>
       </c>
       <c r="R27" s="133"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5171,18 +5070,18 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="87">
-        <v>438804.50782654097</v>
-      </c>
-      <c r="G28" s="180">
-        <f>518000-G32-G33</f>
-        <v>439030</v>
+        <v>469011.1744932076</v>
+      </c>
+      <c r="G28" s="201">
+        <f>554000-G32-G33</f>
+        <v>469553.33333333331</v>
       </c>
       <c r="H28" s="126">
         <f t="shared" si="0"/>
-        <v>-225.49217345903162</v>
+        <v>-542.15884012571769</v>
       </c>
       <c r="I28" s="105">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J28" s="87">
         <f t="shared" si="2"/>
@@ -5192,17 +5091,17 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L28" s="186"/>
+      <c r="L28" s="180"/>
       <c r="M28" s="6">
         <f t="shared" si="4"/>
-        <v>469011.1744932076</v>
+        <v>468694.50782654091</v>
       </c>
       <c r="N28" s="10">
         <f t="shared" si="1"/>
-        <v>497151.84496280004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>496816.17829613335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5217,15 +5116,12 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="87">
-        <v>438609.70395670005</v>
-      </c>
-      <c r="G29" s="181">
-        <f>558645-G42-G43-G44</f>
-        <v>438700</v>
-      </c>
+        <v>469146.37062336667</v>
+      </c>
+      <c r="G29" s="202"/>
       <c r="H29" s="127">
         <f t="shared" si="0"/>
-        <v>-90.296043299953453</v>
+        <v>469146.37062336667</v>
       </c>
       <c r="I29" s="105">
         <v>7</v>
@@ -5238,17 +5134,17 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L29" s="186"/>
+      <c r="L29" s="180"/>
       <c r="M29" s="6">
         <f t="shared" si="4"/>
-        <v>469146.37062336667</v>
+        <v>938383.0372900333</v>
       </c>
       <c r="N29" s="10">
         <f t="shared" si="1"/>
-        <v>497295.15286076866</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>994686.0195274353</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="122" t="s">
         <v>96</v>
       </c>
@@ -5263,11 +5159,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="87">
-        <v>40230.000000000007</v>
-      </c>
-      <c r="G30" s="180">
+        <v>43020.000000000007</v>
+      </c>
+      <c r="G30" s="201">
         <f>F30</f>
-        <v>40230.000000000007</v>
+        <v>43020.000000000007</v>
       </c>
       <c r="H30" s="126">
         <f t="shared" si="0"/>
@@ -5282,7 +5178,7 @@
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L30" s="186"/>
+      <c r="L30" s="180"/>
       <c r="M30" s="6">
         <f t="shared" si="4"/>
         <v>43020.000000000007</v>
@@ -5292,7 +5188,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="122" t="s">
         <v>96</v>
       </c>
@@ -5307,11 +5203,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="87">
-        <v>40975.000000000007</v>
-      </c>
-      <c r="G31" s="180">
+        <v>43816.666666666672</v>
+      </c>
+      <c r="G31" s="201">
         <f>F31</f>
-        <v>40975.000000000007</v>
+        <v>43816.666666666672</v>
       </c>
       <c r="H31" s="126">
         <f t="shared" si="0"/>
@@ -5326,7 +5222,7 @@
         <f t="shared" si="3"/>
         <v>38500.000000000007</v>
       </c>
-      <c r="L31" s="186"/>
+      <c r="L31" s="180"/>
       <c r="M31" s="6">
         <f t="shared" si="4"/>
         <v>43816.666666666672</v>
@@ -5336,7 +5232,7 @@
         <v>46445.666666666672</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="122" t="s">
         <v>96</v>
       </c>
@@ -5351,11 +5247,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="87">
-        <v>33525</v>
-      </c>
-      <c r="G32" s="180">
+        <v>35850</v>
+      </c>
+      <c r="G32" s="201">
         <f>F32</f>
-        <v>33525</v>
+        <v>35850</v>
       </c>
       <c r="H32" s="126">
         <f t="shared" si="0"/>
@@ -5380,7 +5276,7 @@
         <v>38001</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="122" t="s">
         <v>96</v>
       </c>
@@ -5395,11 +5291,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="87">
-        <v>45445</v>
-      </c>
-      <c r="G33" s="180">
+        <v>48596.666666666664</v>
+      </c>
+      <c r="G33" s="201">
         <f t="shared" ref="G33:G34" si="5">F33</f>
-        <v>45445</v>
+        <v>48596.666666666664</v>
       </c>
       <c r="H33" s="126">
         <f t="shared" si="0"/>
@@ -5424,7 +5320,7 @@
         <v>51512.466666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="122" t="s">
         <v>96</v>
       </c>
@@ -5439,11 +5335,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="87">
-        <v>40230.000000000007</v>
-      </c>
-      <c r="G34" s="180">
+        <v>43020.000000000007</v>
+      </c>
+      <c r="G34" s="201">
         <f t="shared" si="5"/>
-        <v>40230.000000000007</v>
+        <v>43020.000000000007</v>
       </c>
       <c r="H34" s="126">
         <f t="shared" si="0"/>
@@ -5468,7 +5364,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="122" t="s">
         <v>96</v>
       </c>
@@ -5483,11 +5379,11 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="10">
-        <v>37250</v>
-      </c>
-      <c r="G35" s="181">
+        <v>39833.333333333336</v>
+      </c>
+      <c r="G35" s="202">
         <f>F35</f>
-        <v>37250</v>
+        <v>39833.333333333336</v>
       </c>
       <c r="H35" s="126">
         <f t="shared" si="0"/>
@@ -5512,7 +5408,7 @@
         <v>42223.333333333336</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="122" t="s">
         <v>96</v>
       </c>
@@ -5527,11 +5423,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="87">
-        <v>37250</v>
-      </c>
-      <c r="G36" s="180">
+        <v>39833.333333333336</v>
+      </c>
+      <c r="G36" s="201">
         <f>F36</f>
-        <v>37250</v>
+        <v>39833.333333333336</v>
       </c>
       <c r="H36" s="126">
         <f t="shared" si="0"/>
@@ -5556,7 +5452,7 @@
         <v>42223.333333333336</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="122" t="s">
         <v>96</v>
       </c>
@@ -5571,11 +5467,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="87">
-        <v>36505</v>
-      </c>
-      <c r="G37" s="180">
+        <v>39036.666666666664</v>
+      </c>
+      <c r="G37" s="201">
         <f t="shared" ref="G37:G41" si="6">F37</f>
-        <v>36505</v>
+        <v>39036.666666666664</v>
       </c>
       <c r="H37" s="126">
         <f t="shared" si="0"/>
@@ -5600,7 +5496,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="122" t="s">
         <v>96</v>
       </c>
@@ -5615,11 +5511,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="87">
-        <v>36505</v>
-      </c>
-      <c r="G38" s="180">
+        <v>39036.666666666664</v>
+      </c>
+      <c r="G38" s="201">
         <f t="shared" si="6"/>
-        <v>36505</v>
+        <v>39036.666666666664</v>
       </c>
       <c r="H38" s="126">
         <f t="shared" si="0"/>
@@ -5644,7 +5540,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="122" t="s">
         <v>96</v>
       </c>
@@ -5659,11 +5555,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="87">
-        <v>43955</v>
-      </c>
-      <c r="G39" s="180">
+        <v>47003.333333333336</v>
+      </c>
+      <c r="G39" s="201">
         <f t="shared" si="6"/>
-        <v>43955</v>
+        <v>47003.333333333336</v>
       </c>
       <c r="H39" s="126">
         <f t="shared" si="0"/>
@@ -5688,7 +5584,7 @@
         <v>49823.533333333333</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="122" t="s">
         <v>96</v>
       </c>
@@ -5703,11 +5599,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="87">
-        <v>42464.999999999993</v>
-      </c>
-      <c r="G40" s="180">
+        <v>45409.999999999993</v>
+      </c>
+      <c r="G40" s="201">
         <f t="shared" si="6"/>
-        <v>42464.999999999993</v>
+        <v>45409.999999999993</v>
       </c>
       <c r="H40" s="126">
         <f t="shared" si="0"/>
@@ -5732,7 +5628,7 @@
         <v>48134.599999999991</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="122" t="s">
         <v>96</v>
       </c>
@@ -5747,11 +5643,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="87">
-        <v>40230.000000000007</v>
-      </c>
-      <c r="G41" s="180">
+        <v>43020.000000000007</v>
+      </c>
+      <c r="G41" s="201">
         <f t="shared" si="6"/>
-        <v>40230.000000000007</v>
+        <v>43020.000000000007</v>
       </c>
       <c r="H41" s="126">
         <f t="shared" si="0"/>
@@ -5776,7 +5672,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="122" t="s">
         <v>96</v>
       </c>
@@ -5791,15 +5687,12 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="87">
-        <v>40975.000000000007</v>
-      </c>
-      <c r="G42" s="180">
-        <f>F42</f>
-        <v>40975.000000000007</v>
-      </c>
+        <v>43816.666666666672</v>
+      </c>
+      <c r="G42" s="201"/>
       <c r="H42" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43816.666666666672</v>
       </c>
       <c r="I42" s="105"/>
       <c r="J42" s="87">
@@ -5813,14 +5706,14 @@
       <c r="L42" s="151"/>
       <c r="M42" s="6">
         <f t="shared" si="4"/>
-        <v>43816.666666666672</v>
+        <v>87633.333333333343</v>
       </c>
       <c r="N42" s="10">
         <f t="shared" si="1"/>
-        <v>46445.666666666672</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>92891.333333333343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="122" t="s">
         <v>96</v>
       </c>
@@ -5835,15 +5728,12 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="87">
-        <v>33525</v>
-      </c>
-      <c r="G43" s="180">
-        <f t="shared" ref="G43:G44" si="7">F43</f>
-        <v>33525</v>
-      </c>
+        <v>35850</v>
+      </c>
+      <c r="G43" s="201"/>
       <c r="H43" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35850</v>
       </c>
       <c r="I43" s="105"/>
       <c r="J43" s="87">
@@ -5857,18 +5747,18 @@
       <c r="L43" s="151"/>
       <c r="M43" s="6">
         <f t="shared" si="4"/>
-        <v>35850</v>
+        <v>71700</v>
       </c>
       <c r="N43" s="10">
         <f t="shared" si="1"/>
-        <v>38001</v>
+        <v>76002</v>
       </c>
       <c r="P43" s="107">
         <f>L1-K52</f>
-        <v>1233011.0918130009</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>809874.85386599973</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="122" t="s">
         <v>96</v>
       </c>
@@ -5883,15 +5773,12 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="87">
-        <v>45445</v>
-      </c>
-      <c r="G44" s="180">
-        <f t="shared" si="7"/>
-        <v>45445</v>
-      </c>
+        <v>48596.666666666664</v>
+      </c>
+      <c r="G44" s="201"/>
       <c r="H44" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48596.666666666664</v>
       </c>
       <c r="I44" s="105"/>
       <c r="J44" s="87">
@@ -5905,14 +5792,14 @@
       <c r="L44" s="151"/>
       <c r="M44" s="6">
         <f t="shared" si="4"/>
-        <v>48596.666666666664</v>
+        <v>97193.333333333328</v>
       </c>
       <c r="N44" s="10">
         <f t="shared" si="1"/>
-        <v>51512.466666666667</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+        <v>103024.93333333333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="122" t="s">
         <v>96</v>
       </c>
@@ -5927,11 +5814,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="87">
-        <v>40230.000000000007</v>
-      </c>
-      <c r="G45" s="180">
-        <f t="shared" ref="G45:G48" si="8">F45</f>
-        <v>40230.000000000007</v>
+        <v>43020.000000000007</v>
+      </c>
+      <c r="G45" s="201">
+        <f t="shared" ref="G45:G48" si="7">F45</f>
+        <v>43020.000000000007</v>
       </c>
       <c r="H45" s="126">
         <f t="shared" si="0"/>
@@ -5956,7 +5843,7 @@
         <v>45601.200000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="122" t="s">
         <v>96</v>
       </c>
@@ -5971,11 +5858,11 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="87">
-        <v>37250</v>
-      </c>
-      <c r="G46" s="180">
+        <v>42223.333333333336</v>
+      </c>
+      <c r="G46" s="201">
         <f>F46</f>
-        <v>37250</v>
+        <v>42223.333333333336</v>
       </c>
       <c r="H46" s="126">
         <f t="shared" si="0"/>
@@ -6003,7 +5890,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="122" t="s">
         <v>96</v>
       </c>
@@ -6018,11 +5905,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="87">
-        <v>37250</v>
-      </c>
-      <c r="G47" s="180">
-        <f t="shared" si="8"/>
-        <v>37250</v>
+        <v>39833.333333333336</v>
+      </c>
+      <c r="G47" s="201">
+        <f t="shared" si="7"/>
+        <v>39833.333333333336</v>
       </c>
       <c r="H47" s="126">
         <f t="shared" si="0"/>
@@ -6049,10 +5936,10 @@
       <c r="O47" s="133"/>
       <c r="Q47" s="130">
         <f>M3-J52</f>
-        <v>2011536.666666667</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>-888463.33333333314</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="122" t="s">
         <v>96</v>
       </c>
@@ -6067,11 +5954,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="87">
-        <v>36505</v>
-      </c>
-      <c r="G48" s="180">
-        <f t="shared" si="8"/>
-        <v>36505</v>
+        <v>39036.666666666664</v>
+      </c>
+      <c r="G48" s="201">
+        <f t="shared" si="7"/>
+        <v>39036.666666666664</v>
       </c>
       <c r="H48" s="126">
         <f t="shared" si="0"/>
@@ -6096,7 +5983,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="122" t="s">
         <v>96</v>
       </c>
@@ -6112,11 +5999,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="87">
-        <v>36505</v>
-      </c>
-      <c r="G49" s="180">
+        <v>39036.666666666664</v>
+      </c>
+      <c r="G49" s="201">
         <f>F49</f>
-        <v>36505</v>
+        <v>39036.666666666664</v>
       </c>
       <c r="H49" s="126">
         <f t="shared" si="0"/>
@@ -6141,7 +6028,7 @@
         <v>41378.866666666661</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="122" t="s">
         <v>96</v>
       </c>
@@ -6156,11 +6043,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="87">
-        <v>43955</v>
-      </c>
-      <c r="G50" s="181">
+        <v>47003.333333333336</v>
+      </c>
+      <c r="G50" s="202">
         <f>F50</f>
-        <v>43955</v>
+        <v>47003.333333333336</v>
       </c>
       <c r="H50" s="126">
         <f t="shared" si="0"/>
@@ -6185,7 +6072,7 @@
         <v>49823.533333333333</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="122" t="s">
         <v>96</v>
       </c>
@@ -6200,11 +6087,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="87">
-        <v>42464.999999999993</v>
-      </c>
-      <c r="G51" s="180">
+        <v>45409.999999999993</v>
+      </c>
+      <c r="G51" s="201">
         <f>F51</f>
-        <v>42464.999999999993</v>
+        <v>45409.999999999993</v>
       </c>
       <c r="H51" s="126">
         <f t="shared" si="0"/>
@@ -6229,7 +6116,7 @@
         <v>48134.599999999991</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="88"/>
       <c r="B52" s="88"/>
       <c r="C52" s="88"/>
@@ -6238,13 +6125,13 @@
         <f>SUM(E7:E51)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F52" s="183">
+      <c r="F52" s="177">
         <f>SUM(F7:F51)</f>
-        <v>6694001.5113024348</v>
-      </c>
-      <c r="G52" s="183">
+        <v>8893975.0570354722</v>
+      </c>
+      <c r="G52" s="177">
         <f>SUM(G7:G51)</f>
-        <v>6941937.3369510006</v>
+        <v>9627966.0681870002</v>
       </c>
       <c r="H52" s="88"/>
       <c r="I52" s="88"/>
@@ -6254,57 +6141,57 @@
       </c>
       <c r="K52" s="89">
         <f>SUM(K7:K51)</f>
-        <v>6951656.2981869997</v>
-      </c>
-      <c r="L52" s="185">
+        <v>6870053.5061339997</v>
+      </c>
+      <c r="L52" s="179">
         <f>SUM(L7:L51)</f>
-        <v>1204999</v>
+        <v>1210000</v>
       </c>
       <c r="M52" s="90">
         <f>SUM(M7:M51)</f>
-        <v>8875386.1392051</v>
+        <v>8234525.8283158056</v>
       </c>
       <c r="N52" s="89">
         <f>SUM(N7:N51)</f>
-        <v>9407909.3075574059</v>
+        <v>8728597.3780147545</v>
       </c>
       <c r="P52" s="130"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="133">
         <f>K52-L1</f>
-        <v>-1233011.0918130009</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="226"/>
-      <c r="D54" s="226"/>
-      <c r="E54" s="226"/>
-      <c r="F54" s="226"/>
-      <c r="G54" s="226"/>
-      <c r="H54" s="226"/>
-      <c r="I54" s="226"/>
-      <c r="J54" s="226"/>
-      <c r="K54" s="226"/>
-      <c r="L54" s="226"/>
-      <c r="M54" s="226"/>
-      <c r="N54" s="226"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="226"/>
-      <c r="D55" s="226"/>
-      <c r="E55" s="226"/>
-      <c r="F55" s="226"/>
-      <c r="G55" s="226"/>
-      <c r="H55" s="226"/>
-      <c r="I55" s="226"/>
-      <c r="J55" s="226"/>
-      <c r="K55" s="226"/>
-      <c r="L55" s="226"/>
-      <c r="M55" s="226"/>
-      <c r="N55" s="226"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-809874.85386599973</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="231"/>
+      <c r="D54" s="231"/>
+      <c r="E54" s="231"/>
+      <c r="F54" s="231"/>
+      <c r="G54" s="231"/>
+      <c r="H54" s="231"/>
+      <c r="I54" s="231"/>
+      <c r="J54" s="231"/>
+      <c r="K54" s="231"/>
+      <c r="L54" s="231"/>
+      <c r="M54" s="231"/>
+      <c r="N54" s="231"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="231"/>
+      <c r="D55" s="231"/>
+      <c r="E55" s="231"/>
+      <c r="F55" s="231"/>
+      <c r="G55" s="231"/>
+      <c r="H55" s="231"/>
+      <c r="I55" s="231"/>
+      <c r="J55" s="231"/>
+      <c r="K55" s="231"/>
+      <c r="L55" s="231"/>
+      <c r="M55" s="231"/>
+      <c r="N55" s="231"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="153"/>
       <c r="D56" s="153"/>
       <c r="E56" s="153"/>
@@ -6318,109 +6205,108 @@
       <c r="M56" s="153"/>
       <c r="N56" s="153"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="226" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="231" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="226"/>
-      <c r="E57" s="226"/>
-      <c r="F57" s="226"/>
-      <c r="G57" s="226"/>
-      <c r="H57" s="226"/>
-      <c r="I57" s="226"/>
-      <c r="J57" s="226"/>
-      <c r="K57" s="226"/>
-      <c r="L57" s="226"/>
-      <c r="M57" s="226"/>
-      <c r="N57" s="226"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="226"/>
-      <c r="D58" s="226"/>
-      <c r="E58" s="226"/>
-      <c r="F58" s="226"/>
-      <c r="G58" s="226"/>
-      <c r="H58" s="226"/>
-      <c r="I58" s="226"/>
-      <c r="J58" s="226"/>
-      <c r="K58" s="226"/>
-      <c r="L58" s="226"/>
-      <c r="M58" s="226"/>
-      <c r="N58" s="226"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="226"/>
-      <c r="D59" s="226"/>
-      <c r="E59" s="226"/>
-      <c r="F59" s="226"/>
-      <c r="G59" s="226"/>
-      <c r="H59" s="226"/>
-      <c r="I59" s="226"/>
-      <c r="J59" s="226"/>
-      <c r="K59" s="226"/>
-      <c r="L59" s="226"/>
-      <c r="M59" s="226"/>
-      <c r="N59" s="226"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="226"/>
-      <c r="D60" s="226"/>
-      <c r="E60" s="226"/>
-      <c r="F60" s="226"/>
-      <c r="G60" s="226"/>
-      <c r="H60" s="226"/>
-      <c r="I60" s="226"/>
-      <c r="J60" s="226"/>
-      <c r="K60" s="226"/>
-      <c r="L60" s="226"/>
-      <c r="M60" s="226"/>
-      <c r="N60" s="226"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="226"/>
-      <c r="D61" s="226"/>
-      <c r="E61" s="226"/>
-      <c r="F61" s="226"/>
-      <c r="G61" s="226"/>
-      <c r="H61" s="226"/>
-      <c r="I61" s="226"/>
-      <c r="J61" s="226"/>
-      <c r="K61" s="226"/>
-      <c r="L61" s="226"/>
-      <c r="M61" s="226"/>
-      <c r="N61" s="226"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="226"/>
-      <c r="D62" s="226"/>
-      <c r="E62" s="226"/>
-      <c r="F62" s="226"/>
-      <c r="G62" s="226"/>
-      <c r="H62" s="226"/>
-      <c r="I62" s="226"/>
-      <c r="J62" s="226"/>
-      <c r="K62" s="226"/>
-      <c r="L62" s="226"/>
-      <c r="M62" s="226"/>
-      <c r="N62" s="226"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="226"/>
-      <c r="D63" s="226"/>
-      <c r="E63" s="226"/>
-      <c r="F63" s="226"/>
-      <c r="G63" s="226"/>
-      <c r="H63" s="226"/>
-      <c r="I63" s="226"/>
-      <c r="J63" s="226"/>
-      <c r="K63" s="226"/>
-      <c r="L63" s="226"/>
-      <c r="M63" s="226"/>
-      <c r="N63" s="226"/>
+      <c r="D57" s="231"/>
+      <c r="E57" s="231"/>
+      <c r="F57" s="231"/>
+      <c r="G57" s="231"/>
+      <c r="H57" s="231"/>
+      <c r="I57" s="231"/>
+      <c r="J57" s="231"/>
+      <c r="K57" s="231"/>
+      <c r="L57" s="231"/>
+      <c r="M57" s="231"/>
+      <c r="N57" s="231"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="231"/>
+      <c r="D58" s="231"/>
+      <c r="E58" s="231"/>
+      <c r="F58" s="231"/>
+      <c r="G58" s="231"/>
+      <c r="H58" s="231"/>
+      <c r="I58" s="231"/>
+      <c r="J58" s="231"/>
+      <c r="K58" s="231"/>
+      <c r="L58" s="231"/>
+      <c r="M58" s="231"/>
+      <c r="N58" s="231"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="231"/>
+      <c r="D59" s="231"/>
+      <c r="E59" s="231"/>
+      <c r="F59" s="231"/>
+      <c r="G59" s="231"/>
+      <c r="H59" s="231"/>
+      <c r="I59" s="231"/>
+      <c r="J59" s="231"/>
+      <c r="K59" s="231"/>
+      <c r="L59" s="231"/>
+      <c r="M59" s="231"/>
+      <c r="N59" s="231"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="231"/>
+      <c r="D60" s="231"/>
+      <c r="E60" s="231"/>
+      <c r="F60" s="231"/>
+      <c r="G60" s="231"/>
+      <c r="H60" s="231"/>
+      <c r="I60" s="231"/>
+      <c r="J60" s="231"/>
+      <c r="K60" s="231"/>
+      <c r="L60" s="231"/>
+      <c r="M60" s="231"/>
+      <c r="N60" s="231"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="231"/>
+      <c r="D61" s="231"/>
+      <c r="E61" s="231"/>
+      <c r="F61" s="231"/>
+      <c r="G61" s="231"/>
+      <c r="H61" s="231"/>
+      <c r="I61" s="231"/>
+      <c r="J61" s="231"/>
+      <c r="K61" s="231"/>
+      <c r="L61" s="231"/>
+      <c r="M61" s="231"/>
+      <c r="N61" s="231"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="231"/>
+      <c r="D62" s="231"/>
+      <c r="E62" s="231"/>
+      <c r="F62" s="231"/>
+      <c r="G62" s="231"/>
+      <c r="H62" s="231"/>
+      <c r="I62" s="231"/>
+      <c r="J62" s="231"/>
+      <c r="K62" s="231"/>
+      <c r="L62" s="231"/>
+      <c r="M62" s="231"/>
+      <c r="N62" s="231"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="231"/>
+      <c r="D63" s="231"/>
+      <c r="E63" s="231"/>
+      <c r="F63" s="231"/>
+      <c r="G63" s="231"/>
+      <c r="H63" s="231"/>
+      <c r="I63" s="231"/>
+      <c r="J63" s="231"/>
+      <c r="K63" s="231"/>
+      <c r="L63" s="231"/>
+      <c r="M63" s="231"/>
+      <c r="N63" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
@@ -6438,6 +6324,7 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6447,86 +6334,86 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="174">
+      <c r="D5" s="171">
         <v>-447223.45918396302</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D6" s="171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D7" s="171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D8" s="171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="174">
+      <c r="D11" s="171">
         <v>451182</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="174">
+      <c r="D12" s="171">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="174">
+      <c r="D13" s="171">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="174">
+      <c r="D14" s="171">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
         <v>148</v>
       </c>
@@ -6536,67 +6423,67 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="174">
+      <c r="D17" s="171">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="174">
+      <c r="D18" s="171">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="174">
+      <c r="D19" s="171">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="174">
+      <c r="D20" s="171">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>151</v>
       </c>
-      <c r="D21" s="174">
+      <c r="D21" s="171">
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C22" s="250" t="s">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="257" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="253">
+      <c r="D22" s="260">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C23" s="251"/>
-      <c r="D23" s="254"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" s="251"/>
-      <c r="D24" s="254"/>
-    </row>
-    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="252"/>
-      <c r="D25" s="255"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="258"/>
+      <c r="D23" s="261"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="258"/>
+      <c r="D24" s="261"/>
+    </row>
+    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="259"/>
+      <c r="D25" s="262"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6611,16 +6498,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -6644,7 +6531,7 @@
       </c>
       <c r="O1" s="51"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="48"/>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
@@ -6663,7 +6550,7 @@
       <c r="N2" s="48"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="48"/>
       <c r="B3" s="50"/>
       <c r="C3" s="50"/>
@@ -6686,7 +6573,7 @@
       </c>
       <c r="O3" s="53"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48"/>
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
@@ -6707,11 +6594,11 @@
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="256" t="s">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="263" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="256" t="s">
+      <c r="B5" s="263" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="54" t="s">
@@ -6723,7 +6610,7 @@
       <c r="E5" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="256" t="s">
+      <c r="F5" s="263" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="36" t="s">
@@ -6745,16 +6632,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="40"/>
-      <c r="N5" s="256" t="s">
+      <c r="N5" s="263" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="256" t="s">
+      <c r="O5" s="263" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="257"/>
-      <c r="B6" s="257"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="264"/>
+      <c r="B6" s="264"/>
       <c r="C6" s="55" t="s">
         <v>80</v>
       </c>
@@ -6764,7 +6651,7 @@
       <c r="E6" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="43" t="s">
         <v>81</v>
       </c>
@@ -6784,10 +6671,10 @@
         <v>84</v>
       </c>
       <c r="M6" s="46"/>
-      <c r="N6" s="257"/>
-      <c r="O6" s="257"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="264"/>
+      <c r="O6" s="264"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>1</v>
       </c>
@@ -6833,7 +6720,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>2</v>
       </c>
@@ -6879,7 +6766,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>3</v>
       </c>
@@ -6925,7 +6812,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>4</v>
       </c>
@@ -6971,7 +6858,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>5</v>
       </c>
@@ -7017,7 +6904,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>6</v>
       </c>
@@ -7063,7 +6950,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>7</v>
       </c>
@@ -7109,7 +6996,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>8</v>
       </c>
@@ -7155,7 +7042,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>9</v>
       </c>
@@ -7201,7 +7088,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>10</v>
       </c>
@@ -7247,7 +7134,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>11</v>
       </c>
@@ -7293,7 +7180,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>12</v>
       </c>
@@ -7339,7 +7226,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>13</v>
       </c>
@@ -7385,7 +7272,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>14</v>
       </c>
@@ -7431,7 +7318,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>15</v>
       </c>
@@ -7477,7 +7364,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>16</v>
       </c>
@@ -7523,7 +7410,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>17</v>
       </c>
@@ -7569,7 +7456,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>18</v>
       </c>
@@ -7615,7 +7502,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>19</v>
       </c>
@@ -7661,7 +7548,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>20</v>
       </c>
@@ -7707,7 +7594,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>21</v>
       </c>
@@ -7753,7 +7640,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>22</v>
       </c>
@@ -7799,7 +7686,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
@@ -7816,7 +7703,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="56">
@@ -7857,7 +7744,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="32"/>
       <c r="F33" s="32"/>
     </row>
